--- a/KatalonData/RADTestData/MRF.xlsx
+++ b/KatalonData/RADTestData/MRF.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
   <workbookPr defaultThemeVersion="166925"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <mc:AlternateContent>
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\t465179\Documents\git\VPS-Katalon\VPS-Katalon\KatalonData\RADTestData\"/>
     </mc:Choice>
@@ -24,7 +24,7 @@
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
+    <ext uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
     </ext>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
@@ -43,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="787" uniqueCount="163">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1271" uniqueCount="285">
   <si>
     <t>Result</t>
   </si>
@@ -532,12 +532,379 @@
   </si>
   <si>
     <t>Mon Aug 03 15:30:51 EDT 2026</t>
+  </si>
+  <si>
+    <t>Fail</t>
+  </si>
+  <si>
+    <t>Sat Aug 15 14:50:46 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Aug 15 14:51:47 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Aug 15 14:52:52 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Aug 15 14:53:41 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Aug 15 14:54:13 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Aug 15 14:54:44 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Aug 15 14:55:22 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Aug 15 14:55:58 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Aug 15 14:56:33 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Aug 15 14:57:08 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Aug 15 14:57:37 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Aug 15 14:58:03 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Aug 15 14:58:31 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Aug 15 14:59:00 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Aug 15 14:59:28 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Aug 15 14:59:57 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Aug 15 15:00:32 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Aug 15 15:01:02 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Aug 15 15:01:36 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Aug 15 15:02:39 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Aug 15 15:03:20 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Aug 15 15:03:52 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Aug 15 15:04:21 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Aug 15 15:04:51 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Aug 15 15:05:18 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Aug 15 15:05:48 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Aug 15 15:06:18 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Aug 15 15:06:47 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Aug 15 15:07:18 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Aug 15 15:07:51 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Aug 15 15:08:35 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Aug 15 15:09:19 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Aug 15 15:10:01 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Aug 15 15:10:49 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Aug 15 15:11:43 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Aug 15 15:12:12 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Aug 15 15:12:49 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Aug 15 15:13:21 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Aug 15 15:13:51 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Aug 15 15:14:31 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Aug 15 15:15:01 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Aug 15 15:15:29 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Aug 15 15:15:58 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Aug 15 15:16:27 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Aug 15 15:16:56 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Aug 15 15:17:28 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Aug 15 15:17:56 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Aug 15 15:18:26 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Aug 15 15:18:56 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Aug 15 15:19:24 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Aug 15 15:19:53 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Aug 15 15:20:21 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Aug 15 15:20:49 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Aug 15 15:21:18 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Aug 15 15:21:46 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Aug 15 15:22:16 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Aug 15 15:22:56 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Aug 15 15:23:26 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Aug 15 15:23:56 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Aug 15 15:24:27 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Aug 15 15:24:58 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Aug 15 15:25:27 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Aug 15 15:25:55 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Aug 15 15:26:28 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Aug 15 15:27:00 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Aug 15 15:27:29 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Aug 15 15:27:56 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Aug 15 15:28:35 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Aug 15 15:29:05 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Aug 15 15:29:38 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Aug 15 15:30:06 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Aug 15 15:30:38 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Aug 15 15:31:11 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Aug 15 15:31:39 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Aug 15 15:32:11 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Aug 15 15:32:50 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Aug 15 15:33:21 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Aug 15 15:33:58 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Aug 15 15:34:28 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Aug 15 15:35:01 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Aug 15 15:35:47 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Aug 15 15:36:18 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Aug 15 15:36:46 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Aug 15 15:37:14 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Aug 15 15:37:41 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Aug 15 15:38:09 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Aug 15 15:38:41 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Aug 15 15:39:10 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Aug 15 15:39:39 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Aug 15 15:40:08 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Aug 15 15:40:42 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Aug 15 15:41:14 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Aug 15 15:41:44 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Aug 15 15:42:14 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Aug 15 15:42:49 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Aug 15 15:43:19 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Aug 15 15:43:46 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Aug 15 15:44:15 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Aug 15 15:44:53 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Aug 15 15:45:22 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Aug 15 15:45:51 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Aug 15 15:46:24 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Aug 15 15:46:56 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Aug 15 15:47:28 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Aug 15 15:47:51 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Aug 15 15:48:21 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Aug 15 15:48:49 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Aug 15 15:49:25 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Aug 15 15:49:53 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Aug 15 15:50:26 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Aug 15 15:50:55 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Aug 15 15:51:25 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Aug 15 15:51:56 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Aug 15 15:52:30 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Aug 15 15:52:59 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Aug 15 15:53:27 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Aug 15 15:54:02 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Aug 15 15:54:43 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Aug 15 15:55:20 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Aug 15 15:56:01 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Aug 15 15:56:42 IST 2026</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <numFmts count="0"/>
   <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -910,15 +1277,15 @@
   <dimension ref="A1:H8"/>
   <sheetFormatPr defaultColWidth="9.19921875" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="1" width="9.19921875" style="1" collapsed="1"/>
-    <col min="2" max="2" width="26.73046875" style="1" bestFit="1" customWidth="1" collapsed="1"/>
-    <col min="3" max="3" width="9.19921875" style="1" collapsed="1"/>
-    <col min="4" max="4" width="44.53125" style="1" customWidth="1" collapsed="1"/>
-    <col min="5" max="5" width="35.53125" style="1" customWidth="1" collapsed="1"/>
-    <col min="6" max="6" width="15.265625" style="1" customWidth="1" collapsed="1"/>
-    <col min="7" max="7" width="17.265625" style="1" customWidth="1" collapsed="1"/>
-    <col min="8" max="8" width="19.53125" style="1" customWidth="1" collapsed="1"/>
-    <col min="9" max="16384" width="9.19921875" style="1" collapsed="1"/>
+    <col min="1" max="1" style="1" width="9.19921875" collapsed="true"/>
+    <col min="2" max="2" bestFit="true" customWidth="true" style="1" width="26.73046875" collapsed="true"/>
+    <col min="3" max="3" style="1" width="9.19921875" collapsed="true"/>
+    <col min="4" max="4" customWidth="true" style="1" width="44.53125" collapsed="true"/>
+    <col min="5" max="5" customWidth="true" style="1" width="35.53125" collapsed="true"/>
+    <col min="6" max="6" customWidth="true" style="1" width="15.265625" collapsed="true"/>
+    <col min="7" max="7" customWidth="true" style="1" width="17.265625" collapsed="true"/>
+    <col min="8" max="8" customWidth="true" style="1" width="19.53125" collapsed="true"/>
+    <col min="9" max="16384" style="1" width="9.19921875" collapsed="true"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.45">
@@ -952,7 +1319,7 @@
         <v>35</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>58</v>
+        <v>164</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>32</v>
@@ -975,7 +1342,7 @@
         <v>35</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>59</v>
+        <v>165</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>32</v>
@@ -998,7 +1365,7 @@
         <v>35</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>60</v>
+        <v>166</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>32</v>
@@ -1024,7 +1391,7 @@
         <v>35</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>61</v>
+        <v>167</v>
       </c>
       <c r="C5" s="1" t="s">
         <v>32</v>
@@ -1050,7 +1417,7 @@
         <v>35</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>62</v>
+        <v>168</v>
       </c>
       <c r="C6" s="1" t="s">
         <v>32</v>
@@ -1076,7 +1443,7 @@
         <v>35</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>63</v>
+        <v>169</v>
       </c>
       <c r="C7" s="1" t="s">
         <v>32</v>
@@ -1102,7 +1469,7 @@
         <v>35</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>64</v>
+        <v>170</v>
       </c>
       <c r="C8" s="1" t="s">
         <v>32</v>
@@ -1135,14 +1502,14 @@
   <dimension ref="A1:H21"/>
   <sheetFormatPr defaultColWidth="9.19921875" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="1" width="14.53125" style="1" customWidth="1" collapsed="1"/>
-    <col min="2" max="2" width="26.73046875" style="1" bestFit="1" customWidth="1" collapsed="1"/>
-    <col min="3" max="3" width="13.46484375" style="1" customWidth="1" collapsed="1"/>
-    <col min="4" max="4" width="52.46484375" style="1" customWidth="1" collapsed="1"/>
-    <col min="5" max="5" width="32.46484375" style="1" customWidth="1" collapsed="1"/>
-    <col min="6" max="7" width="9.19921875" style="1" collapsed="1"/>
-    <col min="8" max="8" width="13" style="1" customWidth="1" collapsed="1"/>
-    <col min="9" max="16384" width="9.19921875" style="1" collapsed="1"/>
+    <col min="1" max="1" customWidth="true" style="1" width="14.53125" collapsed="true"/>
+    <col min="2" max="2" bestFit="true" customWidth="true" style="1" width="26.73046875" collapsed="true"/>
+    <col min="3" max="3" customWidth="true" style="1" width="13.46484375" collapsed="true"/>
+    <col min="4" max="4" customWidth="true" style="1" width="52.46484375" collapsed="true"/>
+    <col min="5" max="5" customWidth="true" style="1" width="32.46484375" collapsed="true"/>
+    <col min="6" max="7" style="1" width="9.19921875" collapsed="true"/>
+    <col min="8" max="8" customWidth="true" style="1" width="13.0" collapsed="true"/>
+    <col min="9" max="16384" style="1" width="9.19921875" collapsed="true"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.45">
@@ -1176,7 +1543,7 @@
         <v>35</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>65</v>
+        <v>171</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>32</v>
@@ -1193,7 +1560,7 @@
         <v>35</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>66</v>
+        <v>172</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>32</v>
@@ -1210,7 +1577,7 @@
         <v>35</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>67</v>
+        <v>173</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>32</v>
@@ -1227,7 +1594,7 @@
         <v>35</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>68</v>
+        <v>174</v>
       </c>
       <c r="C5" s="1" t="s">
         <v>32</v>
@@ -1247,7 +1614,7 @@
         <v>35</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>69</v>
+        <v>175</v>
       </c>
       <c r="C6" s="1" t="s">
         <v>32</v>
@@ -1267,7 +1634,7 @@
         <v>35</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>70</v>
+        <v>176</v>
       </c>
       <c r="C7" s="1" t="s">
         <v>32</v>
@@ -1287,7 +1654,7 @@
         <v>35</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>71</v>
+        <v>177</v>
       </c>
       <c r="C8" s="1" t="s">
         <v>32</v>
@@ -1307,7 +1674,7 @@
         <v>35</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>72</v>
+        <v>178</v>
       </c>
       <c r="C9" s="1" t="s">
         <v>32</v>
@@ -1327,7 +1694,7 @@
         <v>35</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>73</v>
+        <v>179</v>
       </c>
       <c r="C10" s="1" t="s">
         <v>32</v>
@@ -1347,7 +1714,7 @@
         <v>35</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>74</v>
+        <v>180</v>
       </c>
       <c r="C11" s="1" t="s">
         <v>32</v>
@@ -1367,7 +1734,7 @@
         <v>35</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>75</v>
+        <v>181</v>
       </c>
       <c r="C12" s="1" t="s">
         <v>32</v>
@@ -1387,7 +1754,7 @@
         <v>35</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>76</v>
+        <v>182</v>
       </c>
       <c r="C13" s="1" t="s">
         <v>32</v>
@@ -1407,7 +1774,7 @@
         <v>35</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>77</v>
+        <v>183</v>
       </c>
       <c r="C14" s="1" t="s">
         <v>32</v>
@@ -1427,7 +1794,7 @@
         <v>35</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>78</v>
+        <v>184</v>
       </c>
       <c r="C15" s="1" t="s">
         <v>32</v>
@@ -1444,7 +1811,7 @@
         <v>35</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>79</v>
+        <v>185</v>
       </c>
       <c r="C16" s="1" t="s">
         <v>32</v>
@@ -1467,7 +1834,7 @@
         <v>35</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>80</v>
+        <v>186</v>
       </c>
       <c r="C17" s="1" t="s">
         <v>32</v>
@@ -1487,7 +1854,7 @@
         <v>35</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>81</v>
+        <v>187</v>
       </c>
       <c r="C18" s="1" t="s">
         <v>32</v>
@@ -1515,7 +1882,7 @@
         <v>35</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>82</v>
+        <v>188</v>
       </c>
       <c r="C20" s="1" t="s">
         <v>32</v>
@@ -1554,15 +1921,15 @@
   <dimension ref="A1:H7"/>
   <sheetFormatPr defaultColWidth="9.19921875" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="1" width="9.19921875" style="1" collapsed="1"/>
-    <col min="2" max="2" width="35" style="1" customWidth="1" collapsed="1"/>
-    <col min="3" max="3" width="19.19921875" style="1" customWidth="1" collapsed="1"/>
-    <col min="4" max="4" width="24.46484375" style="1" customWidth="1" collapsed="1"/>
-    <col min="5" max="5" width="27" style="1" bestFit="1" customWidth="1" collapsed="1"/>
-    <col min="6" max="6" width="9.19921875" style="1" collapsed="1"/>
-    <col min="7" max="7" width="17" style="1" customWidth="1" collapsed="1"/>
-    <col min="8" max="8" width="16.265625" style="1" customWidth="1" collapsed="1"/>
-    <col min="9" max="16384" width="9.19921875" style="1" collapsed="1"/>
+    <col min="1" max="1" style="1" width="9.19921875" collapsed="true"/>
+    <col min="2" max="2" customWidth="true" style="1" width="35.0" collapsed="true"/>
+    <col min="3" max="3" customWidth="true" style="1" width="19.19921875" collapsed="true"/>
+    <col min="4" max="4" customWidth="true" style="1" width="24.46484375" collapsed="true"/>
+    <col min="5" max="5" bestFit="true" customWidth="true" style="1" width="27.0" collapsed="true"/>
+    <col min="6" max="6" style="1" width="9.19921875" collapsed="true"/>
+    <col min="7" max="7" customWidth="true" style="1" width="17.0" collapsed="true"/>
+    <col min="8" max="8" customWidth="true" style="1" width="16.265625" collapsed="true"/>
+    <col min="9" max="16384" style="1" width="9.19921875" collapsed="true"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.45">
@@ -1596,7 +1963,7 @@
         <v>35</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>83</v>
+        <v>189</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>32</v>
@@ -1619,7 +1986,7 @@
         <v>35</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>84</v>
+        <v>190</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>32</v>
@@ -1639,7 +2006,7 @@
         <v>35</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>85</v>
+        <v>191</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>32</v>
@@ -1662,7 +2029,7 @@
         <v>35</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>86</v>
+        <v>192</v>
       </c>
       <c r="C5" s="1" t="s">
         <v>32</v>
@@ -1685,7 +2052,7 @@
         <v>35</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>87</v>
+        <v>193</v>
       </c>
       <c r="C6" s="1" t="s">
         <v>32</v>
@@ -1708,7 +2075,7 @@
         <v>35</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>88</v>
+        <v>194</v>
       </c>
       <c r="C7" s="1" t="s">
         <v>32</v>
@@ -1740,17 +2107,17 @@
   <dimension ref="A1:J64"/>
   <sheetFormatPr defaultColWidth="9.19921875" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="1" width="9.19921875" style="1" collapsed="1"/>
-    <col min="2" max="2" width="26" style="1" bestFit="1" customWidth="1" collapsed="1"/>
-    <col min="3" max="3" width="12.33203125" style="1" customWidth="1" collapsed="1"/>
-    <col min="4" max="4" width="31.73046875" style="1" customWidth="1" collapsed="1"/>
-    <col min="5" max="5" width="39.53125" style="1" customWidth="1" collapsed="1"/>
-    <col min="6" max="6" width="9.19921875" style="1" collapsed="1"/>
-    <col min="7" max="7" width="19.796875" style="1" customWidth="1" collapsed="1"/>
-    <col min="8" max="8" width="14.46484375" style="1" customWidth="1" collapsed="1"/>
-    <col min="9" max="9" width="12.73046875" style="1" customWidth="1" collapsed="1"/>
-    <col min="10" max="10" width="11.19921875" style="1" customWidth="1" collapsed="1"/>
-    <col min="11" max="16384" width="9.19921875" style="1" collapsed="1"/>
+    <col min="1" max="1" style="1" width="9.19921875" collapsed="true"/>
+    <col min="2" max="2" bestFit="true" customWidth="true" style="1" width="26.0" collapsed="true"/>
+    <col min="3" max="3" customWidth="true" style="1" width="12.33203125" collapsed="true"/>
+    <col min="4" max="4" customWidth="true" style="1" width="31.73046875" collapsed="true"/>
+    <col min="5" max="5" customWidth="true" style="1" width="39.53125" collapsed="true"/>
+    <col min="6" max="6" style="1" width="9.19921875" collapsed="true"/>
+    <col min="7" max="7" customWidth="true" style="1" width="19.796875" collapsed="true"/>
+    <col min="8" max="8" customWidth="true" style="1" width="14.46484375" collapsed="true"/>
+    <col min="9" max="9" customWidth="true" style="1" width="12.73046875" collapsed="true"/>
+    <col min="10" max="10" customWidth="true" style="1" width="11.19921875" collapsed="true"/>
+    <col min="11" max="16384" style="1" width="9.19921875" collapsed="true"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:10" x14ac:dyDescent="0.45">
@@ -1790,7 +2157,7 @@
         <v>35</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>89</v>
+        <v>195</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>32</v>
@@ -1810,7 +2177,7 @@
         <v>35</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>90</v>
+        <v>196</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>32</v>
@@ -1833,7 +2200,7 @@
         <v>35</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>91</v>
+        <v>197</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>32</v>
@@ -1856,7 +2223,7 @@
         <v>35</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>92</v>
+        <v>198</v>
       </c>
       <c r="C5" s="1" t="s">
         <v>32</v>
@@ -1879,7 +2246,7 @@
         <v>35</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>93</v>
+        <v>199</v>
       </c>
       <c r="C6" s="1" t="s">
         <v>32</v>
@@ -1902,7 +2269,7 @@
         <v>35</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>94</v>
+        <v>200</v>
       </c>
       <c r="C7" s="1" t="s">
         <v>32</v>
@@ -1922,7 +2289,7 @@
         <v>35</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>95</v>
+        <v>201</v>
       </c>
       <c r="C8" s="1" t="s">
         <v>32</v>
@@ -1945,7 +2312,7 @@
         <v>35</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>96</v>
+        <v>202</v>
       </c>
       <c r="C9" s="1" t="s">
         <v>32</v>
@@ -1968,7 +2335,7 @@
         <v>35</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>97</v>
+        <v>203</v>
       </c>
       <c r="C10" s="1" t="s">
         <v>32</v>
@@ -1991,7 +2358,7 @@
         <v>35</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>98</v>
+        <v>204</v>
       </c>
       <c r="C11" s="1" t="s">
         <v>32</v>
@@ -2014,7 +2381,7 @@
         <v>35</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>99</v>
+        <v>205</v>
       </c>
       <c r="C12" s="1" t="s">
         <v>32</v>
@@ -2034,7 +2401,7 @@
         <v>35</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>100</v>
+        <v>206</v>
       </c>
       <c r="C13" s="1" t="s">
         <v>32</v>
@@ -2057,7 +2424,7 @@
         <v>35</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>101</v>
+        <v>207</v>
       </c>
       <c r="C14" s="1" t="s">
         <v>32</v>
@@ -2080,7 +2447,7 @@
         <v>35</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>102</v>
+        <v>208</v>
       </c>
       <c r="C15" s="1" t="s">
         <v>32</v>
@@ -2103,7 +2470,7 @@
         <v>35</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>103</v>
+        <v>209</v>
       </c>
       <c r="C16" s="1" t="s">
         <v>32</v>
@@ -2126,7 +2493,7 @@
         <v>35</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>104</v>
+        <v>210</v>
       </c>
       <c r="C17" s="1" t="s">
         <v>32</v>
@@ -2149,7 +2516,7 @@
         <v>35</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>105</v>
+        <v>211</v>
       </c>
       <c r="C18" s="1" t="s">
         <v>32</v>
@@ -2172,7 +2539,7 @@
         <v>35</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>106</v>
+        <v>212</v>
       </c>
       <c r="C19" s="1" t="s">
         <v>32</v>
@@ -2192,7 +2559,7 @@
         <v>35</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>107</v>
+        <v>213</v>
       </c>
       <c r="C20" s="1" t="s">
         <v>32</v>
@@ -2212,7 +2579,7 @@
         <v>35</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>108</v>
+        <v>214</v>
       </c>
       <c r="C21" s="1" t="s">
         <v>32</v>
@@ -2235,7 +2602,7 @@
         <v>35</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>109</v>
+        <v>215</v>
       </c>
       <c r="C22" s="1" t="s">
         <v>32</v>
@@ -2258,7 +2625,7 @@
         <v>35</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>110</v>
+        <v>216</v>
       </c>
       <c r="C23" s="1" t="s">
         <v>32</v>
@@ -2278,7 +2645,7 @@
         <v>35</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>111</v>
+        <v>217</v>
       </c>
       <c r="C24" s="1" t="s">
         <v>32</v>
@@ -2301,7 +2668,7 @@
         <v>35</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>112</v>
+        <v>218</v>
       </c>
       <c r="C25" s="1" t="s">
         <v>32</v>
@@ -2327,7 +2694,7 @@
         <v>35</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>113</v>
+        <v>219</v>
       </c>
       <c r="C26" s="1" t="s">
         <v>32</v>
@@ -2350,7 +2717,7 @@
         <v>35</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>114</v>
+        <v>220</v>
       </c>
       <c r="C27" s="1" t="s">
         <v>32</v>
@@ -2370,7 +2737,7 @@
         <v>35</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>115</v>
+        <v>221</v>
       </c>
       <c r="C28" s="1" t="s">
         <v>32</v>
@@ -2393,7 +2760,7 @@
         <v>35</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>116</v>
+        <v>222</v>
       </c>
       <c r="C29" s="1" t="s">
         <v>32</v>
@@ -2416,7 +2783,7 @@
         <v>35</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>117</v>
+        <v>223</v>
       </c>
       <c r="C30" s="1" t="s">
         <v>32</v>
@@ -2439,7 +2806,7 @@
         <v>35</v>
       </c>
       <c r="B31" s="1" t="s">
-        <v>118</v>
+        <v>224</v>
       </c>
       <c r="C31" s="1" t="s">
         <v>32</v>
@@ -2459,7 +2826,7 @@
         <v>35</v>
       </c>
       <c r="B32" s="1" t="s">
-        <v>119</v>
+        <v>225</v>
       </c>
       <c r="C32" s="1" t="s">
         <v>32</v>
@@ -2479,7 +2846,7 @@
         <v>35</v>
       </c>
       <c r="B33" s="1" t="s">
-        <v>120</v>
+        <v>226</v>
       </c>
       <c r="C33" s="1" t="s">
         <v>32</v>
@@ -2502,7 +2869,7 @@
         <v>35</v>
       </c>
       <c r="B34" s="1" t="s">
-        <v>121</v>
+        <v>227</v>
       </c>
       <c r="C34" s="1" t="s">
         <v>32</v>
@@ -2525,7 +2892,7 @@
         <v>35</v>
       </c>
       <c r="B35" s="1" t="s">
-        <v>122</v>
+        <v>228</v>
       </c>
       <c r="C35" s="1" t="s">
         <v>32</v>
@@ -2545,7 +2912,7 @@
         <v>35</v>
       </c>
       <c r="B36" s="1" t="s">
-        <v>123</v>
+        <v>229</v>
       </c>
       <c r="C36" s="1" t="s">
         <v>32</v>
@@ -2568,7 +2935,7 @@
         <v>35</v>
       </c>
       <c r="B37" s="1" t="s">
-        <v>124</v>
+        <v>230</v>
       </c>
       <c r="C37" s="1" t="s">
         <v>32</v>
@@ -2594,7 +2961,7 @@
         <v>35</v>
       </c>
       <c r="B38" s="1" t="s">
-        <v>125</v>
+        <v>231</v>
       </c>
       <c r="C38" s="1" t="s">
         <v>32</v>
@@ -2617,7 +2984,7 @@
         <v>35</v>
       </c>
       <c r="B39" s="1" t="s">
-        <v>126</v>
+        <v>232</v>
       </c>
       <c r="C39" s="1" t="s">
         <v>32</v>
@@ -2637,7 +3004,7 @@
         <v>35</v>
       </c>
       <c r="B40" s="1" t="s">
-        <v>127</v>
+        <v>233</v>
       </c>
       <c r="C40" s="1" t="s">
         <v>32</v>
@@ -2660,7 +3027,7 @@
         <v>35</v>
       </c>
       <c r="B41" s="1" t="s">
-        <v>128</v>
+        <v>234</v>
       </c>
       <c r="C41" s="1" t="s">
         <v>32</v>
@@ -2683,7 +3050,7 @@
         <v>35</v>
       </c>
       <c r="B42" s="1" t="s">
-        <v>129</v>
+        <v>235</v>
       </c>
       <c r="C42" s="1" t="s">
         <v>32</v>
@@ -2706,7 +3073,7 @@
         <v>35</v>
       </c>
       <c r="B43" s="1" t="s">
-        <v>130</v>
+        <v>236</v>
       </c>
       <c r="C43" s="1" t="s">
         <v>32</v>
@@ -2726,7 +3093,7 @@
         <v>35</v>
       </c>
       <c r="B44" s="1" t="s">
-        <v>131</v>
+        <v>237</v>
       </c>
       <c r="C44" s="1" t="s">
         <v>32</v>
@@ -2746,7 +3113,7 @@
         <v>35</v>
       </c>
       <c r="B45" s="1" t="s">
-        <v>132</v>
+        <v>238</v>
       </c>
       <c r="C45" s="1" t="s">
         <v>32</v>
@@ -2769,7 +3136,7 @@
         <v>35</v>
       </c>
       <c r="B46" s="1" t="s">
-        <v>133</v>
+        <v>239</v>
       </c>
       <c r="C46" s="1" t="s">
         <v>32</v>
@@ -2792,7 +3159,7 @@
         <v>35</v>
       </c>
       <c r="B47" s="1" t="s">
-        <v>134</v>
+        <v>240</v>
       </c>
       <c r="C47" s="1" t="s">
         <v>32</v>
@@ -2812,7 +3179,7 @@
         <v>35</v>
       </c>
       <c r="B48" s="1" t="s">
-        <v>135</v>
+        <v>241</v>
       </c>
       <c r="C48" s="1" t="s">
         <v>32</v>
@@ -2835,7 +3202,7 @@
         <v>35</v>
       </c>
       <c r="B49" s="1" t="s">
-        <v>136</v>
+        <v>242</v>
       </c>
       <c r="C49" s="1" t="s">
         <v>32</v>
@@ -2861,7 +3228,7 @@
         <v>35</v>
       </c>
       <c r="B50" s="1" t="s">
-        <v>137</v>
+        <v>243</v>
       </c>
       <c r="C50" s="1" t="s">
         <v>32</v>
@@ -2884,7 +3251,7 @@
         <v>35</v>
       </c>
       <c r="B51" s="1" t="s">
-        <v>138</v>
+        <v>244</v>
       </c>
       <c r="C51" s="1" t="s">
         <v>32</v>
@@ -2904,7 +3271,7 @@
         <v>35</v>
       </c>
       <c r="B52" s="1" t="s">
-        <v>139</v>
+        <v>245</v>
       </c>
       <c r="C52" s="1" t="s">
         <v>32</v>
@@ -2927,7 +3294,7 @@
         <v>35</v>
       </c>
       <c r="B53" s="1" t="s">
-        <v>140</v>
+        <v>246</v>
       </c>
       <c r="C53" s="1" t="s">
         <v>32</v>
@@ -2947,7 +3314,7 @@
         <v>35</v>
       </c>
       <c r="B54" s="1" t="s">
-        <v>157</v>
+        <v>247</v>
       </c>
       <c r="C54" s="1" t="s">
         <v>32</v>
@@ -2987,7 +3354,7 @@
         <v>35</v>
       </c>
       <c r="B56" s="1" t="s">
-        <v>141</v>
+        <v>248</v>
       </c>
       <c r="C56" s="1" t="s">
         <v>32</v>
@@ -3007,7 +3374,7 @@
         <v>35</v>
       </c>
       <c r="B57" s="1" t="s">
-        <v>158</v>
+        <v>249</v>
       </c>
       <c r="C57" s="1" t="s">
         <v>32</v>
@@ -3047,7 +3414,7 @@
         <v>35</v>
       </c>
       <c r="B59" s="1" t="s">
-        <v>142</v>
+        <v>250</v>
       </c>
       <c r="C59" s="1" t="s">
         <v>32</v>
@@ -3067,7 +3434,7 @@
         <v>35</v>
       </c>
       <c r="B60" s="1" t="s">
-        <v>159</v>
+        <v>251</v>
       </c>
       <c r="C60" s="1" t="s">
         <v>32</v>
@@ -3107,7 +3474,7 @@
         <v>35</v>
       </c>
       <c r="B62" s="1" t="s">
-        <v>143</v>
+        <v>252</v>
       </c>
       <c r="C62" s="1" t="s">
         <v>32</v>
@@ -3130,7 +3497,7 @@
         <v>35</v>
       </c>
       <c r="B63" s="1" t="s">
-        <v>144</v>
+        <v>253</v>
       </c>
       <c r="C63" s="1" t="s">
         <v>32</v>
@@ -3153,7 +3520,7 @@
         <v>35</v>
       </c>
       <c r="B64" s="1" t="s">
-        <v>145</v>
+        <v>254</v>
       </c>
       <c r="C64" s="1" t="s">
         <v>32</v>
@@ -3184,12 +3551,12 @@
   <dimension ref="A1:F7"/>
   <sheetFormatPr defaultColWidth="9.19921875" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="1" width="9.19921875" style="1" collapsed="1"/>
-    <col min="2" max="2" width="22.46484375" style="1" customWidth="1" collapsed="1"/>
-    <col min="3" max="3" width="17.265625" style="1" customWidth="1" collapsed="1"/>
-    <col min="4" max="4" width="50.796875" style="1" customWidth="1" collapsed="1"/>
-    <col min="5" max="5" width="46.265625" style="1" customWidth="1" collapsed="1"/>
-    <col min="6" max="16384" width="9.19921875" style="1" collapsed="1"/>
+    <col min="1" max="1" style="1" width="9.19921875" collapsed="true"/>
+    <col min="2" max="2" customWidth="true" style="1" width="22.46484375" collapsed="true"/>
+    <col min="3" max="3" customWidth="true" style="1" width="17.265625" collapsed="true"/>
+    <col min="4" max="4" customWidth="true" style="1" width="50.796875" collapsed="true"/>
+    <col min="5" max="5" customWidth="true" style="1" width="46.265625" collapsed="true"/>
+    <col min="6" max="16384" style="1" width="9.19921875" collapsed="true"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.45">
@@ -3291,12 +3658,12 @@
   <dimension ref="A1:F9"/>
   <sheetFormatPr defaultColWidth="9.19921875" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="1" width="6.53125" style="1" bestFit="1" customWidth="1" collapsed="1"/>
-    <col min="2" max="2" width="26.46484375" style="1" bestFit="1" customWidth="1" collapsed="1"/>
-    <col min="3" max="3" width="14.796875" style="1" customWidth="1" collapsed="1"/>
-    <col min="4" max="4" width="50.796875" style="1" customWidth="1" collapsed="1"/>
-    <col min="5" max="5" width="46.265625" style="1" customWidth="1" collapsed="1"/>
-    <col min="6" max="16384" width="9.19921875" style="1" collapsed="1"/>
+    <col min="1" max="1" bestFit="true" customWidth="true" style="1" width="6.53125" collapsed="true"/>
+    <col min="2" max="2" bestFit="true" customWidth="true" style="1" width="26.46484375" collapsed="true"/>
+    <col min="3" max="3" customWidth="true" style="1" width="14.796875" collapsed="true"/>
+    <col min="4" max="4" customWidth="true" style="1" width="50.796875" collapsed="true"/>
+    <col min="5" max="5" customWidth="true" style="1" width="46.265625" collapsed="true"/>
+    <col min="6" max="16384" style="1" width="9.19921875" collapsed="true"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.45">
@@ -3324,7 +3691,7 @@
         <v>35</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>147</v>
+        <v>272</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>32</v>
@@ -3344,7 +3711,7 @@
         <v>35</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>148</v>
+        <v>273</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>32</v>
@@ -3364,7 +3731,7 @@
         <v>35</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>149</v>
+        <v>274</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>32</v>
@@ -3384,7 +3751,7 @@
         <v>35</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>150</v>
+        <v>275</v>
       </c>
       <c r="C5" s="1" t="s">
         <v>32</v>
@@ -3404,7 +3771,7 @@
         <v>35</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>151</v>
+        <v>276</v>
       </c>
       <c r="C6" s="1" t="s">
         <v>32</v>
@@ -3424,7 +3791,7 @@
         <v>35</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>160</v>
+        <v>277</v>
       </c>
       <c r="C7" s="1" t="s">
         <v>32</v>
@@ -3444,7 +3811,7 @@
         <v>35</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>161</v>
+        <v>278</v>
       </c>
       <c r="C8" s="1" t="s">
         <v>32</v>
@@ -3464,7 +3831,7 @@
         <v>35</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>162</v>
+        <v>279</v>
       </c>
       <c r="C9" s="1" t="s">
         <v>32</v>
@@ -3489,12 +3856,12 @@
   <dimension ref="A1:F6"/>
   <sheetFormatPr defaultColWidth="9.19921875" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="1" width="9.19921875" style="1" collapsed="1"/>
-    <col min="2" max="2" width="27.73046875" style="1" bestFit="1" customWidth="1" collapsed="1"/>
-    <col min="3" max="3" width="15.796875" style="1" customWidth="1" collapsed="1"/>
-    <col min="4" max="4" width="50.796875" style="1" customWidth="1" collapsed="1"/>
-    <col min="5" max="5" width="46.265625" style="1" customWidth="1" collapsed="1"/>
-    <col min="6" max="16384" width="9.19921875" style="1" collapsed="1"/>
+    <col min="1" max="1" style="1" width="9.19921875" collapsed="true"/>
+    <col min="2" max="2" bestFit="true" customWidth="true" style="1" width="27.73046875" collapsed="true"/>
+    <col min="3" max="3" customWidth="true" style="1" width="15.796875" collapsed="true"/>
+    <col min="4" max="4" customWidth="true" style="1" width="50.796875" collapsed="true"/>
+    <col min="5" max="5" customWidth="true" style="1" width="46.265625" collapsed="true"/>
+    <col min="6" max="16384" style="1" width="9.19921875" collapsed="true"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.45">
@@ -3522,7 +3889,7 @@
         <v>35</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>152</v>
+        <v>280</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>32</v>
@@ -3542,7 +3909,7 @@
         <v>35</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>153</v>
+        <v>281</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>32</v>
@@ -3562,7 +3929,7 @@
         <v>35</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>154</v>
+        <v>282</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>32</v>
@@ -3582,7 +3949,7 @@
         <v>35</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>155</v>
+        <v>283</v>
       </c>
       <c r="C5" s="1" t="s">
         <v>32</v>
@@ -3602,7 +3969,7 @@
         <v>35</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>156</v>
+        <v>284</v>
       </c>
       <c r="C6" s="1" t="s">
         <v>32</v>
@@ -3627,12 +3994,12 @@
   <dimension ref="A1:E3"/>
   <sheetFormatPr defaultColWidth="9.19921875" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="1" width="9.19921875" style="1" collapsed="1"/>
-    <col min="2" max="2" width="22.46484375" style="1" customWidth="1" collapsed="1"/>
-    <col min="3" max="3" width="15.796875" style="1" customWidth="1" collapsed="1"/>
-    <col min="4" max="4" width="50.796875" style="1" customWidth="1" collapsed="1"/>
-    <col min="5" max="5" width="46.265625" style="1" customWidth="1" collapsed="1"/>
-    <col min="6" max="16384" width="9.19921875" style="1" collapsed="1"/>
+    <col min="1" max="1" style="1" width="9.19921875" collapsed="true"/>
+    <col min="2" max="2" customWidth="true" style="1" width="22.46484375" collapsed="true"/>
+    <col min="3" max="3" customWidth="true" style="1" width="15.796875" collapsed="true"/>
+    <col min="4" max="4" customWidth="true" style="1" width="50.796875" collapsed="true"/>
+    <col min="5" max="5" customWidth="true" style="1" width="46.265625" collapsed="true"/>
+    <col min="6" max="16384" style="1" width="9.19921875" collapsed="true"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.45">
@@ -3657,7 +4024,7 @@
         <v>35</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>146</v>
+        <v>255</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>32</v>

--- a/KatalonData/RADTestData/MRF.xlsx
+++ b/KatalonData/RADTestData/MRF.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
   <workbookPr defaultThemeVersion="166925"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <mc:AlternateContent>
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\t465179\Documents\git\VPS-Katalon\VPS-Katalon\KatalonData\RADTestData\"/>
     </mc:Choice>
@@ -24,7 +24,7 @@
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
+    <ext uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
     </ext>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
@@ -43,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="787" uniqueCount="163">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1211" uniqueCount="270">
   <si>
     <t>Result</t>
   </si>
@@ -532,12 +532,334 @@
   </si>
   <si>
     <t>Mon Aug 03 15:30:51 EDT 2026</t>
+  </si>
+  <si>
+    <t>Fail</t>
+  </si>
+  <si>
+    <t>Fri Sep 04 17:27:23 EDT 2026</t>
+  </si>
+  <si>
+    <t>Fri Sep 04 17:27:35 EDT 2026</t>
+  </si>
+  <si>
+    <t>Fri Sep 04 17:27:43 EDT 2026</t>
+  </si>
+  <si>
+    <t>Fri Sep 04 17:27:51 EDT 2026</t>
+  </si>
+  <si>
+    <t>Fri Sep 04 17:27:59 EDT 2026</t>
+  </si>
+  <si>
+    <t>Fri Sep 04 17:28:09 EDT 2026</t>
+  </si>
+  <si>
+    <t>Fri Sep 04 17:28:17 EDT 2026</t>
+  </si>
+  <si>
+    <t>Fri Sep 04 17:28:26 EDT 2026</t>
+  </si>
+  <si>
+    <t>Fri Sep 04 17:28:34 EDT 2026</t>
+  </si>
+  <si>
+    <t>Fri Sep 04 17:28:42 EDT 2026</t>
+  </si>
+  <si>
+    <t>Fri Sep 04 17:28:49 EDT 2026</t>
+  </si>
+  <si>
+    <t>Fri Sep 04 17:28:57 EDT 2026</t>
+  </si>
+  <si>
+    <t>Fri Sep 04 17:29:06 EDT 2026</t>
+  </si>
+  <si>
+    <t>Fri Sep 04 17:29:13 EDT 2026</t>
+  </si>
+  <si>
+    <t>Fri Sep 04 17:29:21 EDT 2026</t>
+  </si>
+  <si>
+    <t>Fri Sep 04 17:29:34 EDT 2026</t>
+  </si>
+  <si>
+    <t>Fri Sep 04 17:29:42 EDT 2026</t>
+  </si>
+  <si>
+    <t>Fri Sep 04 17:29:50 EDT 2026</t>
+  </si>
+  <si>
+    <t>Fri Sep 04 17:29:58 EDT 2026</t>
+  </si>
+  <si>
+    <t>Fri Sep 04 17:30:06 EDT 2026</t>
+  </si>
+  <si>
+    <t>Fri Sep 04 17:30:19 EDT 2026</t>
+  </si>
+  <si>
+    <t>Fri Sep 04 17:30:27 EDT 2026</t>
+  </si>
+  <si>
+    <t>Fri Sep 04 17:30:35 EDT 2026</t>
+  </si>
+  <si>
+    <t>Fri Sep 04 17:30:44 EDT 2026</t>
+  </si>
+  <si>
+    <t>Fri Sep 04 17:30:51 EDT 2026</t>
+  </si>
+  <si>
+    <t>Fri Sep 04 17:30:59 EDT 2026</t>
+  </si>
+  <si>
+    <t>Fri Sep 04 17:31:07 EDT 2026</t>
+  </si>
+  <si>
+    <t>Fri Sep 04 17:31:15 EDT 2026</t>
+  </si>
+  <si>
+    <t>Fri Sep 04 17:31:23 EDT 2026</t>
+  </si>
+  <si>
+    <t>Fri Sep 04 17:31:32 EDT 2026</t>
+  </si>
+  <si>
+    <t>Fri Sep 04 17:31:40 EDT 2026</t>
+  </si>
+  <si>
+    <t>Fri Sep 04 17:31:49 EDT 2026</t>
+  </si>
+  <si>
+    <t>Fri Sep 04 17:31:57 EDT 2026</t>
+  </si>
+  <si>
+    <t>Fri Sep 04 17:32:06 EDT 2026</t>
+  </si>
+  <si>
+    <t>Fri Sep 04 17:32:14 EDT 2026</t>
+  </si>
+  <si>
+    <t>Fri Sep 04 17:32:22 EDT 2026</t>
+  </si>
+  <si>
+    <t>Fri Sep 04 17:32:30 EDT 2026</t>
+  </si>
+  <si>
+    <t>Fri Sep 04 17:32:39 EDT 2026</t>
+  </si>
+  <si>
+    <t>Fri Sep 04 17:32:47 EDT 2026</t>
+  </si>
+  <si>
+    <t>Fri Sep 04 17:33:00 EDT 2026</t>
+  </si>
+  <si>
+    <t>Fri Sep 04 17:33:08 EDT 2026</t>
+  </si>
+  <si>
+    <t>Fri Sep 04 17:33:16 EDT 2026</t>
+  </si>
+  <si>
+    <t>Fri Sep 04 17:33:25 EDT 2026</t>
+  </si>
+  <si>
+    <t>Fri Sep 04 17:33:35 EDT 2026</t>
+  </si>
+  <si>
+    <t>Fri Sep 04 17:33:43 EDT 2026</t>
+  </si>
+  <si>
+    <t>Fri Sep 04 17:33:52 EDT 2026</t>
+  </si>
+  <si>
+    <t>Fri Sep 04 17:34:00 EDT 2026</t>
+  </si>
+  <si>
+    <t>Fri Sep 04 17:34:09 EDT 2026</t>
+  </si>
+  <si>
+    <t>Fri Sep 04 17:34:18 EDT 2026</t>
+  </si>
+  <si>
+    <t>Fri Sep 04 17:34:27 EDT 2026</t>
+  </si>
+  <si>
+    <t>Fri Sep 04 17:34:35 EDT 2026</t>
+  </si>
+  <si>
+    <t>Fri Sep 04 17:34:44 EDT 2026</t>
+  </si>
+  <si>
+    <t>Fri Sep 04 17:34:53 EDT 2026</t>
+  </si>
+  <si>
+    <t>Fri Sep 04 17:35:02 EDT 2026</t>
+  </si>
+  <si>
+    <t>Fri Sep 04 17:35:11 EDT 2026</t>
+  </si>
+  <si>
+    <t>Fri Sep 04 17:35:21 EDT 2026</t>
+  </si>
+  <si>
+    <t>Fri Sep 04 17:35:30 EDT 2026</t>
+  </si>
+  <si>
+    <t>Fri Sep 04 17:35:38 EDT 2026</t>
+  </si>
+  <si>
+    <t>Fri Sep 04 17:35:49 EDT 2026</t>
+  </si>
+  <si>
+    <t>Fri Sep 04 17:35:58 EDT 2026</t>
+  </si>
+  <si>
+    <t>Fri Sep 04 17:36:07 EDT 2026</t>
+  </si>
+  <si>
+    <t>Fri Sep 04 17:36:15 EDT 2026</t>
+  </si>
+  <si>
+    <t>Fri Sep 04 17:36:24 EDT 2026</t>
+  </si>
+  <si>
+    <t>Fri Sep 04 17:36:33 EDT 2026</t>
+  </si>
+  <si>
+    <t>Fri Sep 04 17:36:42 EDT 2026</t>
+  </si>
+  <si>
+    <t>Fri Sep 04 17:36:51 EDT 2026</t>
+  </si>
+  <si>
+    <t>Fri Sep 04 17:37:00 EDT 2026</t>
+  </si>
+  <si>
+    <t>Fri Sep 04 17:37:08 EDT 2026</t>
+  </si>
+  <si>
+    <t>Fri Sep 04 17:37:17 EDT 2026</t>
+  </si>
+  <si>
+    <t>Fri Sep 04 17:37:25 EDT 2026</t>
+  </si>
+  <si>
+    <t>Fri Sep 04 17:37:34 EDT 2026</t>
+  </si>
+  <si>
+    <t>Fri Sep 04 17:37:44 EDT 2026</t>
+  </si>
+  <si>
+    <t>Fri Sep 04 17:37:53 EDT 2026</t>
+  </si>
+  <si>
+    <t>Fri Sep 04 17:38:01 EDT 2026</t>
+  </si>
+  <si>
+    <t>Fri Sep 04 17:38:10 EDT 2026</t>
+  </si>
+  <si>
+    <t>Fri Sep 04 17:38:19 EDT 2026</t>
+  </si>
+  <si>
+    <t>Fri Sep 04 17:38:28 EDT 2026</t>
+  </si>
+  <si>
+    <t>Fri Sep 04 17:38:37 EDT 2026</t>
+  </si>
+  <si>
+    <t>Fri Sep 04 17:38:45 EDT 2026</t>
+  </si>
+  <si>
+    <t>Fri Sep 04 17:38:55 EDT 2026</t>
+  </si>
+  <si>
+    <t>Fri Sep 04 17:39:04 EDT 2026</t>
+  </si>
+  <si>
+    <t>Fri Sep 04 17:39:13 EDT 2026</t>
+  </si>
+  <si>
+    <t>Fri Sep 04 17:39:21 EDT 2026</t>
+  </si>
+  <si>
+    <t>Fri Sep 04 17:39:30 EDT 2026</t>
+  </si>
+  <si>
+    <t>Fri Sep 04 17:39:38 EDT 2026</t>
+  </si>
+  <si>
+    <t>Fri Sep 04 17:39:46 EDT 2026</t>
+  </si>
+  <si>
+    <t>Fri Sep 04 17:39:54 EDT 2026</t>
+  </si>
+  <si>
+    <t>Fri Sep 04 17:40:07 EDT 2026</t>
+  </si>
+  <si>
+    <t>Fri Sep 04 17:40:15 EDT 2026</t>
+  </si>
+  <si>
+    <t>Fri Sep 04 17:40:24 EDT 2026</t>
+  </si>
+  <si>
+    <t>Fri Sep 04 17:40:33 EDT 2026</t>
+  </si>
+  <si>
+    <t>Fri Sep 04 17:40:42 EDT 2026</t>
+  </si>
+  <si>
+    <t>Fri Sep 04 17:40:51 EDT 2026</t>
+  </si>
+  <si>
+    <t>Fri Sep 04 17:40:59 EDT 2026</t>
+  </si>
+  <si>
+    <t>Fri Sep 04 17:41:08 EDT 2026</t>
+  </si>
+  <si>
+    <t>Fri Sep 04 17:41:16 EDT 2026</t>
+  </si>
+  <si>
+    <t>Fri Sep 04 17:41:24 EDT 2026</t>
+  </si>
+  <si>
+    <t>Fri Sep 04 17:41:32 EDT 2026</t>
+  </si>
+  <si>
+    <t>Fri Sep 04 17:41:40 EDT 2026</t>
+  </si>
+  <si>
+    <t>Fri Sep 04 17:41:49 EDT 2026</t>
+  </si>
+  <si>
+    <t>Fri Sep 04 17:41:57 EDT 2026</t>
+  </si>
+  <si>
+    <t>Fri Sep 04 17:42:14 EDT 2026</t>
+  </si>
+  <si>
+    <t>Fri Sep 04 17:42:31 EDT 2026</t>
+  </si>
+  <si>
+    <t>Fri Sep 04 17:42:47 EDT 2026</t>
+  </si>
+  <si>
+    <t>Fri Sep 04 17:43:04 EDT 2026</t>
+  </si>
+  <si>
+    <t>Fri Sep 04 18:14:46 EDT 2026</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <numFmts count="0"/>
   <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -910,15 +1232,15 @@
   <dimension ref="A1:H8"/>
   <sheetFormatPr defaultColWidth="9.19921875" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="1" width="9.19921875" style="1" collapsed="1"/>
-    <col min="2" max="2" width="26.73046875" style="1" bestFit="1" customWidth="1" collapsed="1"/>
-    <col min="3" max="3" width="9.19921875" style="1" collapsed="1"/>
-    <col min="4" max="4" width="44.53125" style="1" customWidth="1" collapsed="1"/>
-    <col min="5" max="5" width="35.53125" style="1" customWidth="1" collapsed="1"/>
-    <col min="6" max="6" width="15.265625" style="1" customWidth="1" collapsed="1"/>
-    <col min="7" max="7" width="17.265625" style="1" customWidth="1" collapsed="1"/>
-    <col min="8" max="8" width="19.53125" style="1" customWidth="1" collapsed="1"/>
-    <col min="9" max="16384" width="9.19921875" style="1" collapsed="1"/>
+    <col min="1" max="1" style="1" width="9.19921875" collapsed="true"/>
+    <col min="2" max="2" bestFit="true" customWidth="true" style="1" width="26.73046875" collapsed="true"/>
+    <col min="3" max="3" style="1" width="9.19921875" collapsed="true"/>
+    <col min="4" max="4" customWidth="true" style="1" width="44.53125" collapsed="true"/>
+    <col min="5" max="5" customWidth="true" style="1" width="35.53125" collapsed="true"/>
+    <col min="6" max="6" customWidth="true" style="1" width="15.265625" collapsed="true"/>
+    <col min="7" max="7" customWidth="true" style="1" width="17.265625" collapsed="true"/>
+    <col min="8" max="8" customWidth="true" style="1" width="19.53125" collapsed="true"/>
+    <col min="9" max="16384" style="1" width="9.19921875" collapsed="true"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.45">
@@ -952,7 +1274,7 @@
         <v>35</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>58</v>
+        <v>269</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>32</v>
@@ -975,7 +1297,7 @@
         <v>35</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>59</v>
+        <v>165</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>32</v>
@@ -998,7 +1320,7 @@
         <v>35</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>60</v>
+        <v>166</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>32</v>
@@ -1024,7 +1346,7 @@
         <v>35</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>61</v>
+        <v>167</v>
       </c>
       <c r="C5" s="1" t="s">
         <v>32</v>
@@ -1050,7 +1372,7 @@
         <v>35</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>62</v>
+        <v>168</v>
       </c>
       <c r="C6" s="1" t="s">
         <v>32</v>
@@ -1076,7 +1398,7 @@
         <v>35</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>63</v>
+        <v>169</v>
       </c>
       <c r="C7" s="1" t="s">
         <v>32</v>
@@ -1102,7 +1424,7 @@
         <v>35</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>64</v>
+        <v>170</v>
       </c>
       <c r="C8" s="1" t="s">
         <v>32</v>
@@ -1135,14 +1457,14 @@
   <dimension ref="A1:H21"/>
   <sheetFormatPr defaultColWidth="9.19921875" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="1" width="14.53125" style="1" customWidth="1" collapsed="1"/>
-    <col min="2" max="2" width="26.73046875" style="1" bestFit="1" customWidth="1" collapsed="1"/>
-    <col min="3" max="3" width="13.46484375" style="1" customWidth="1" collapsed="1"/>
-    <col min="4" max="4" width="52.46484375" style="1" customWidth="1" collapsed="1"/>
-    <col min="5" max="5" width="32.46484375" style="1" customWidth="1" collapsed="1"/>
-    <col min="6" max="7" width="9.19921875" style="1" collapsed="1"/>
-    <col min="8" max="8" width="13" style="1" customWidth="1" collapsed="1"/>
-    <col min="9" max="16384" width="9.19921875" style="1" collapsed="1"/>
+    <col min="1" max="1" customWidth="true" style="1" width="14.53125" collapsed="true"/>
+    <col min="2" max="2" bestFit="true" customWidth="true" style="1" width="26.73046875" collapsed="true"/>
+    <col min="3" max="3" customWidth="true" style="1" width="13.46484375" collapsed="true"/>
+    <col min="4" max="4" customWidth="true" style="1" width="52.46484375" collapsed="true"/>
+    <col min="5" max="5" customWidth="true" style="1" width="32.46484375" collapsed="true"/>
+    <col min="6" max="7" style="1" width="9.19921875" collapsed="true"/>
+    <col min="8" max="8" customWidth="true" style="1" width="13.0" collapsed="true"/>
+    <col min="9" max="16384" style="1" width="9.19921875" collapsed="true"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.45">
@@ -1176,7 +1498,7 @@
         <v>35</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>65</v>
+        <v>171</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>32</v>
@@ -1193,7 +1515,7 @@
         <v>35</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>66</v>
+        <v>172</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>32</v>
@@ -1210,7 +1532,7 @@
         <v>35</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>67</v>
+        <v>173</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>32</v>
@@ -1227,7 +1549,7 @@
         <v>35</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>68</v>
+        <v>174</v>
       </c>
       <c r="C5" s="1" t="s">
         <v>32</v>
@@ -1247,7 +1569,7 @@
         <v>35</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>69</v>
+        <v>175</v>
       </c>
       <c r="C6" s="1" t="s">
         <v>32</v>
@@ -1267,7 +1589,7 @@
         <v>35</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>70</v>
+        <v>176</v>
       </c>
       <c r="C7" s="1" t="s">
         <v>32</v>
@@ -1287,7 +1609,7 @@
         <v>35</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>71</v>
+        <v>177</v>
       </c>
       <c r="C8" s="1" t="s">
         <v>32</v>
@@ -1307,7 +1629,7 @@
         <v>35</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>72</v>
+        <v>178</v>
       </c>
       <c r="C9" s="1" t="s">
         <v>32</v>
@@ -1327,7 +1649,7 @@
         <v>35</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>73</v>
+        <v>179</v>
       </c>
       <c r="C10" s="1" t="s">
         <v>32</v>
@@ -1347,7 +1669,7 @@
         <v>35</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>74</v>
+        <v>180</v>
       </c>
       <c r="C11" s="1" t="s">
         <v>32</v>
@@ -1367,7 +1689,7 @@
         <v>35</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>75</v>
+        <v>181</v>
       </c>
       <c r="C12" s="1" t="s">
         <v>32</v>
@@ -1387,7 +1709,7 @@
         <v>35</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>76</v>
+        <v>182</v>
       </c>
       <c r="C13" s="1" t="s">
         <v>32</v>
@@ -1407,7 +1729,7 @@
         <v>35</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>77</v>
+        <v>183</v>
       </c>
       <c r="C14" s="1" t="s">
         <v>32</v>
@@ -1427,7 +1749,7 @@
         <v>35</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>78</v>
+        <v>184</v>
       </c>
       <c r="C15" s="1" t="s">
         <v>32</v>
@@ -1444,7 +1766,7 @@
         <v>35</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>79</v>
+        <v>185</v>
       </c>
       <c r="C16" s="1" t="s">
         <v>32</v>
@@ -1467,7 +1789,7 @@
         <v>35</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>80</v>
+        <v>186</v>
       </c>
       <c r="C17" s="1" t="s">
         <v>32</v>
@@ -1487,7 +1809,7 @@
         <v>35</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>81</v>
+        <v>187</v>
       </c>
       <c r="C18" s="1" t="s">
         <v>32</v>
@@ -1515,7 +1837,7 @@
         <v>35</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>82</v>
+        <v>188</v>
       </c>
       <c r="C20" s="1" t="s">
         <v>32</v>
@@ -1554,15 +1876,15 @@
   <dimension ref="A1:H7"/>
   <sheetFormatPr defaultColWidth="9.19921875" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="1" width="9.19921875" style="1" collapsed="1"/>
-    <col min="2" max="2" width="35" style="1" customWidth="1" collapsed="1"/>
-    <col min="3" max="3" width="19.19921875" style="1" customWidth="1" collapsed="1"/>
-    <col min="4" max="4" width="24.46484375" style="1" customWidth="1" collapsed="1"/>
-    <col min="5" max="5" width="27" style="1" bestFit="1" customWidth="1" collapsed="1"/>
-    <col min="6" max="6" width="9.19921875" style="1" collapsed="1"/>
-    <col min="7" max="7" width="17" style="1" customWidth="1" collapsed="1"/>
-    <col min="8" max="8" width="16.265625" style="1" customWidth="1" collapsed="1"/>
-    <col min="9" max="16384" width="9.19921875" style="1" collapsed="1"/>
+    <col min="1" max="1" style="1" width="9.19921875" collapsed="true"/>
+    <col min="2" max="2" customWidth="true" style="1" width="35.0" collapsed="true"/>
+    <col min="3" max="3" customWidth="true" style="1" width="19.19921875" collapsed="true"/>
+    <col min="4" max="4" customWidth="true" style="1" width="24.46484375" collapsed="true"/>
+    <col min="5" max="5" bestFit="true" customWidth="true" style="1" width="27.0" collapsed="true"/>
+    <col min="6" max="6" style="1" width="9.19921875" collapsed="true"/>
+    <col min="7" max="7" customWidth="true" style="1" width="17.0" collapsed="true"/>
+    <col min="8" max="8" customWidth="true" style="1" width="16.265625" collapsed="true"/>
+    <col min="9" max="16384" style="1" width="9.19921875" collapsed="true"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.45">
@@ -1596,7 +1918,7 @@
         <v>35</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>83</v>
+        <v>189</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>32</v>
@@ -1619,7 +1941,7 @@
         <v>35</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>84</v>
+        <v>190</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>32</v>
@@ -1639,7 +1961,7 @@
         <v>35</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>85</v>
+        <v>191</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>32</v>
@@ -1662,7 +1984,7 @@
         <v>35</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>86</v>
+        <v>192</v>
       </c>
       <c r="C5" s="1" t="s">
         <v>32</v>
@@ -1685,7 +2007,7 @@
         <v>35</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>87</v>
+        <v>193</v>
       </c>
       <c r="C6" s="1" t="s">
         <v>32</v>
@@ -1708,7 +2030,7 @@
         <v>35</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>88</v>
+        <v>194</v>
       </c>
       <c r="C7" s="1" t="s">
         <v>32</v>
@@ -1740,17 +2062,17 @@
   <dimension ref="A1:J64"/>
   <sheetFormatPr defaultColWidth="9.19921875" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="1" width="9.19921875" style="1" collapsed="1"/>
-    <col min="2" max="2" width="26" style="1" bestFit="1" customWidth="1" collapsed="1"/>
-    <col min="3" max="3" width="12.33203125" style="1" customWidth="1" collapsed="1"/>
-    <col min="4" max="4" width="31.73046875" style="1" customWidth="1" collapsed="1"/>
-    <col min="5" max="5" width="39.53125" style="1" customWidth="1" collapsed="1"/>
-    <col min="6" max="6" width="9.19921875" style="1" collapsed="1"/>
-    <col min="7" max="7" width="19.796875" style="1" customWidth="1" collapsed="1"/>
-    <col min="8" max="8" width="14.46484375" style="1" customWidth="1" collapsed="1"/>
-    <col min="9" max="9" width="12.73046875" style="1" customWidth="1" collapsed="1"/>
-    <col min="10" max="10" width="11.19921875" style="1" customWidth="1" collapsed="1"/>
-    <col min="11" max="16384" width="9.19921875" style="1" collapsed="1"/>
+    <col min="1" max="1" style="1" width="9.19921875" collapsed="true"/>
+    <col min="2" max="2" bestFit="true" customWidth="true" style="1" width="26.0" collapsed="true"/>
+    <col min="3" max="3" customWidth="true" style="1" width="12.33203125" collapsed="true"/>
+    <col min="4" max="4" customWidth="true" style="1" width="31.73046875" collapsed="true"/>
+    <col min="5" max="5" customWidth="true" style="1" width="39.53125" collapsed="true"/>
+    <col min="6" max="6" style="1" width="9.19921875" collapsed="true"/>
+    <col min="7" max="7" customWidth="true" style="1" width="19.796875" collapsed="true"/>
+    <col min="8" max="8" customWidth="true" style="1" width="14.46484375" collapsed="true"/>
+    <col min="9" max="9" customWidth="true" style="1" width="12.73046875" collapsed="true"/>
+    <col min="10" max="10" customWidth="true" style="1" width="11.19921875" collapsed="true"/>
+    <col min="11" max="16384" style="1" width="9.19921875" collapsed="true"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:10" x14ac:dyDescent="0.45">
@@ -1790,7 +2112,7 @@
         <v>35</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>89</v>
+        <v>195</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>32</v>
@@ -1810,7 +2132,7 @@
         <v>35</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>90</v>
+        <v>196</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>32</v>
@@ -1833,7 +2155,7 @@
         <v>35</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>91</v>
+        <v>197</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>32</v>
@@ -1856,7 +2178,7 @@
         <v>35</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>92</v>
+        <v>198</v>
       </c>
       <c r="C5" s="1" t="s">
         <v>32</v>
@@ -1879,7 +2201,7 @@
         <v>35</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>93</v>
+        <v>199</v>
       </c>
       <c r="C6" s="1" t="s">
         <v>32</v>
@@ -1902,7 +2224,7 @@
         <v>35</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>94</v>
+        <v>200</v>
       </c>
       <c r="C7" s="1" t="s">
         <v>32</v>
@@ -1922,7 +2244,7 @@
         <v>35</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>95</v>
+        <v>201</v>
       </c>
       <c r="C8" s="1" t="s">
         <v>32</v>
@@ -1945,7 +2267,7 @@
         <v>35</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>96</v>
+        <v>202</v>
       </c>
       <c r="C9" s="1" t="s">
         <v>32</v>
@@ -1968,7 +2290,7 @@
         <v>35</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>97</v>
+        <v>203</v>
       </c>
       <c r="C10" s="1" t="s">
         <v>32</v>
@@ -1991,7 +2313,7 @@
         <v>35</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>98</v>
+        <v>204</v>
       </c>
       <c r="C11" s="1" t="s">
         <v>32</v>
@@ -2014,7 +2336,7 @@
         <v>35</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>99</v>
+        <v>205</v>
       </c>
       <c r="C12" s="1" t="s">
         <v>32</v>
@@ -2034,7 +2356,7 @@
         <v>35</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>100</v>
+        <v>206</v>
       </c>
       <c r="C13" s="1" t="s">
         <v>32</v>
@@ -2057,7 +2379,7 @@
         <v>35</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>101</v>
+        <v>207</v>
       </c>
       <c r="C14" s="1" t="s">
         <v>32</v>
@@ -2080,7 +2402,7 @@
         <v>35</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>102</v>
+        <v>208</v>
       </c>
       <c r="C15" s="1" t="s">
         <v>32</v>
@@ -2103,7 +2425,7 @@
         <v>35</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>103</v>
+        <v>209</v>
       </c>
       <c r="C16" s="1" t="s">
         <v>32</v>
@@ -2126,7 +2448,7 @@
         <v>35</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>104</v>
+        <v>210</v>
       </c>
       <c r="C17" s="1" t="s">
         <v>32</v>
@@ -2149,7 +2471,7 @@
         <v>35</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>105</v>
+        <v>211</v>
       </c>
       <c r="C18" s="1" t="s">
         <v>32</v>
@@ -2172,7 +2494,7 @@
         <v>35</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>106</v>
+        <v>212</v>
       </c>
       <c r="C19" s="1" t="s">
         <v>32</v>
@@ -2192,7 +2514,7 @@
         <v>35</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>107</v>
+        <v>213</v>
       </c>
       <c r="C20" s="1" t="s">
         <v>32</v>
@@ -2212,7 +2534,7 @@
         <v>35</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>108</v>
+        <v>214</v>
       </c>
       <c r="C21" s="1" t="s">
         <v>32</v>
@@ -2235,7 +2557,7 @@
         <v>35</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>109</v>
+        <v>215</v>
       </c>
       <c r="C22" s="1" t="s">
         <v>32</v>
@@ -2258,7 +2580,7 @@
         <v>35</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>110</v>
+        <v>216</v>
       </c>
       <c r="C23" s="1" t="s">
         <v>32</v>
@@ -2278,7 +2600,7 @@
         <v>35</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>111</v>
+        <v>217</v>
       </c>
       <c r="C24" s="1" t="s">
         <v>32</v>
@@ -2301,7 +2623,7 @@
         <v>35</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>112</v>
+        <v>218</v>
       </c>
       <c r="C25" s="1" t="s">
         <v>32</v>
@@ -2327,7 +2649,7 @@
         <v>35</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>113</v>
+        <v>219</v>
       </c>
       <c r="C26" s="1" t="s">
         <v>32</v>
@@ -2350,7 +2672,7 @@
         <v>35</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>114</v>
+        <v>220</v>
       </c>
       <c r="C27" s="1" t="s">
         <v>32</v>
@@ -2370,7 +2692,7 @@
         <v>35</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>115</v>
+        <v>221</v>
       </c>
       <c r="C28" s="1" t="s">
         <v>32</v>
@@ -2393,7 +2715,7 @@
         <v>35</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>116</v>
+        <v>222</v>
       </c>
       <c r="C29" s="1" t="s">
         <v>32</v>
@@ -2416,7 +2738,7 @@
         <v>35</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>117</v>
+        <v>223</v>
       </c>
       <c r="C30" s="1" t="s">
         <v>32</v>
@@ -2439,7 +2761,7 @@
         <v>35</v>
       </c>
       <c r="B31" s="1" t="s">
-        <v>118</v>
+        <v>224</v>
       </c>
       <c r="C31" s="1" t="s">
         <v>32</v>
@@ -2459,7 +2781,7 @@
         <v>35</v>
       </c>
       <c r="B32" s="1" t="s">
-        <v>119</v>
+        <v>225</v>
       </c>
       <c r="C32" s="1" t="s">
         <v>32</v>
@@ -2479,7 +2801,7 @@
         <v>35</v>
       </c>
       <c r="B33" s="1" t="s">
-        <v>120</v>
+        <v>226</v>
       </c>
       <c r="C33" s="1" t="s">
         <v>32</v>
@@ -2502,7 +2824,7 @@
         <v>35</v>
       </c>
       <c r="B34" s="1" t="s">
-        <v>121</v>
+        <v>227</v>
       </c>
       <c r="C34" s="1" t="s">
         <v>32</v>
@@ -2525,7 +2847,7 @@
         <v>35</v>
       </c>
       <c r="B35" s="1" t="s">
-        <v>122</v>
+        <v>228</v>
       </c>
       <c r="C35" s="1" t="s">
         <v>32</v>
@@ -2545,7 +2867,7 @@
         <v>35</v>
       </c>
       <c r="B36" s="1" t="s">
-        <v>123</v>
+        <v>229</v>
       </c>
       <c r="C36" s="1" t="s">
         <v>32</v>
@@ -2568,7 +2890,7 @@
         <v>35</v>
       </c>
       <c r="B37" s="1" t="s">
-        <v>124</v>
+        <v>230</v>
       </c>
       <c r="C37" s="1" t="s">
         <v>32</v>
@@ -2594,7 +2916,7 @@
         <v>35</v>
       </c>
       <c r="B38" s="1" t="s">
-        <v>125</v>
+        <v>231</v>
       </c>
       <c r="C38" s="1" t="s">
         <v>32</v>
@@ -2617,7 +2939,7 @@
         <v>35</v>
       </c>
       <c r="B39" s="1" t="s">
-        <v>126</v>
+        <v>232</v>
       </c>
       <c r="C39" s="1" t="s">
         <v>32</v>
@@ -2637,7 +2959,7 @@
         <v>35</v>
       </c>
       <c r="B40" s="1" t="s">
-        <v>127</v>
+        <v>233</v>
       </c>
       <c r="C40" s="1" t="s">
         <v>32</v>
@@ -2660,7 +2982,7 @@
         <v>35</v>
       </c>
       <c r="B41" s="1" t="s">
-        <v>128</v>
+        <v>234</v>
       </c>
       <c r="C41" s="1" t="s">
         <v>32</v>
@@ -2683,7 +3005,7 @@
         <v>35</v>
       </c>
       <c r="B42" s="1" t="s">
-        <v>129</v>
+        <v>235</v>
       </c>
       <c r="C42" s="1" t="s">
         <v>32</v>
@@ -2706,7 +3028,7 @@
         <v>35</v>
       </c>
       <c r="B43" s="1" t="s">
-        <v>130</v>
+        <v>236</v>
       </c>
       <c r="C43" s="1" t="s">
         <v>32</v>
@@ -2726,7 +3048,7 @@
         <v>35</v>
       </c>
       <c r="B44" s="1" t="s">
-        <v>131</v>
+        <v>237</v>
       </c>
       <c r="C44" s="1" t="s">
         <v>32</v>
@@ -2746,7 +3068,7 @@
         <v>35</v>
       </c>
       <c r="B45" s="1" t="s">
-        <v>132</v>
+        <v>238</v>
       </c>
       <c r="C45" s="1" t="s">
         <v>32</v>
@@ -2769,7 +3091,7 @@
         <v>35</v>
       </c>
       <c r="B46" s="1" t="s">
-        <v>133</v>
+        <v>239</v>
       </c>
       <c r="C46" s="1" t="s">
         <v>32</v>
@@ -2792,7 +3114,7 @@
         <v>35</v>
       </c>
       <c r="B47" s="1" t="s">
-        <v>134</v>
+        <v>240</v>
       </c>
       <c r="C47" s="1" t="s">
         <v>32</v>
@@ -2812,7 +3134,7 @@
         <v>35</v>
       </c>
       <c r="B48" s="1" t="s">
-        <v>135</v>
+        <v>241</v>
       </c>
       <c r="C48" s="1" t="s">
         <v>32</v>
@@ -2835,7 +3157,7 @@
         <v>35</v>
       </c>
       <c r="B49" s="1" t="s">
-        <v>136</v>
+        <v>242</v>
       </c>
       <c r="C49" s="1" t="s">
         <v>32</v>
@@ -2861,7 +3183,7 @@
         <v>35</v>
       </c>
       <c r="B50" s="1" t="s">
-        <v>137</v>
+        <v>243</v>
       </c>
       <c r="C50" s="1" t="s">
         <v>32</v>
@@ -2884,7 +3206,7 @@
         <v>35</v>
       </c>
       <c r="B51" s="1" t="s">
-        <v>138</v>
+        <v>244</v>
       </c>
       <c r="C51" s="1" t="s">
         <v>32</v>
@@ -2904,7 +3226,7 @@
         <v>35</v>
       </c>
       <c r="B52" s="1" t="s">
-        <v>139</v>
+        <v>245</v>
       </c>
       <c r="C52" s="1" t="s">
         <v>32</v>
@@ -2927,7 +3249,7 @@
         <v>35</v>
       </c>
       <c r="B53" s="1" t="s">
-        <v>140</v>
+        <v>246</v>
       </c>
       <c r="C53" s="1" t="s">
         <v>32</v>
@@ -2947,7 +3269,7 @@
         <v>35</v>
       </c>
       <c r="B54" s="1" t="s">
-        <v>157</v>
+        <v>247</v>
       </c>
       <c r="C54" s="1" t="s">
         <v>32</v>
@@ -2987,7 +3309,7 @@
         <v>35</v>
       </c>
       <c r="B56" s="1" t="s">
-        <v>141</v>
+        <v>248</v>
       </c>
       <c r="C56" s="1" t="s">
         <v>32</v>
@@ -3007,7 +3329,7 @@
         <v>35</v>
       </c>
       <c r="B57" s="1" t="s">
-        <v>158</v>
+        <v>249</v>
       </c>
       <c r="C57" s="1" t="s">
         <v>32</v>
@@ -3047,7 +3369,7 @@
         <v>35</v>
       </c>
       <c r="B59" s="1" t="s">
-        <v>142</v>
+        <v>250</v>
       </c>
       <c r="C59" s="1" t="s">
         <v>32</v>
@@ -3067,7 +3389,7 @@
         <v>35</v>
       </c>
       <c r="B60" s="1" t="s">
-        <v>159</v>
+        <v>251</v>
       </c>
       <c r="C60" s="1" t="s">
         <v>32</v>
@@ -3107,7 +3429,7 @@
         <v>35</v>
       </c>
       <c r="B62" s="1" t="s">
-        <v>143</v>
+        <v>252</v>
       </c>
       <c r="C62" s="1" t="s">
         <v>32</v>
@@ -3130,7 +3452,7 @@
         <v>35</v>
       </c>
       <c r="B63" s="1" t="s">
-        <v>144</v>
+        <v>253</v>
       </c>
       <c r="C63" s="1" t="s">
         <v>32</v>
@@ -3153,7 +3475,7 @@
         <v>35</v>
       </c>
       <c r="B64" s="1" t="s">
-        <v>145</v>
+        <v>254</v>
       </c>
       <c r="C64" s="1" t="s">
         <v>32</v>
@@ -3184,12 +3506,12 @@
   <dimension ref="A1:F7"/>
   <sheetFormatPr defaultColWidth="9.19921875" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="1" width="9.19921875" style="1" collapsed="1"/>
-    <col min="2" max="2" width="22.46484375" style="1" customWidth="1" collapsed="1"/>
-    <col min="3" max="3" width="17.265625" style="1" customWidth="1" collapsed="1"/>
-    <col min="4" max="4" width="50.796875" style="1" customWidth="1" collapsed="1"/>
-    <col min="5" max="5" width="46.265625" style="1" customWidth="1" collapsed="1"/>
-    <col min="6" max="16384" width="9.19921875" style="1" collapsed="1"/>
+    <col min="1" max="1" style="1" width="9.19921875" collapsed="true"/>
+    <col min="2" max="2" customWidth="true" style="1" width="22.46484375" collapsed="true"/>
+    <col min="3" max="3" customWidth="true" style="1" width="17.265625" collapsed="true"/>
+    <col min="4" max="4" customWidth="true" style="1" width="50.796875" collapsed="true"/>
+    <col min="5" max="5" customWidth="true" style="1" width="46.265625" collapsed="true"/>
+    <col min="6" max="16384" style="1" width="9.19921875" collapsed="true"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.45">
@@ -3291,12 +3613,12 @@
   <dimension ref="A1:F9"/>
   <sheetFormatPr defaultColWidth="9.19921875" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="1" width="6.53125" style="1" bestFit="1" customWidth="1" collapsed="1"/>
-    <col min="2" max="2" width="26.46484375" style="1" bestFit="1" customWidth="1" collapsed="1"/>
-    <col min="3" max="3" width="14.796875" style="1" customWidth="1" collapsed="1"/>
-    <col min="4" max="4" width="50.796875" style="1" customWidth="1" collapsed="1"/>
-    <col min="5" max="5" width="46.265625" style="1" customWidth="1" collapsed="1"/>
-    <col min="6" max="16384" width="9.19921875" style="1" collapsed="1"/>
+    <col min="1" max="1" bestFit="true" customWidth="true" style="1" width="6.53125" collapsed="true"/>
+    <col min="2" max="2" bestFit="true" customWidth="true" style="1" width="26.46484375" collapsed="true"/>
+    <col min="3" max="3" customWidth="true" style="1" width="14.796875" collapsed="true"/>
+    <col min="4" max="4" customWidth="true" style="1" width="50.796875" collapsed="true"/>
+    <col min="5" max="5" customWidth="true" style="1" width="46.265625" collapsed="true"/>
+    <col min="6" max="16384" style="1" width="9.19921875" collapsed="true"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.45">
@@ -3324,7 +3646,7 @@
         <v>35</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>147</v>
+        <v>256</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>32</v>
@@ -3344,7 +3666,7 @@
         <v>35</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>148</v>
+        <v>257</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>32</v>
@@ -3364,7 +3686,7 @@
         <v>35</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>149</v>
+        <v>258</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>32</v>
@@ -3384,7 +3706,7 @@
         <v>35</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>150</v>
+        <v>259</v>
       </c>
       <c r="C5" s="1" t="s">
         <v>32</v>
@@ -3404,7 +3726,7 @@
         <v>35</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>151</v>
+        <v>260</v>
       </c>
       <c r="C6" s="1" t="s">
         <v>32</v>
@@ -3424,7 +3746,7 @@
         <v>35</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>160</v>
+        <v>261</v>
       </c>
       <c r="C7" s="1" t="s">
         <v>32</v>
@@ -3444,7 +3766,7 @@
         <v>35</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>161</v>
+        <v>262</v>
       </c>
       <c r="C8" s="1" t="s">
         <v>32</v>
@@ -3464,7 +3786,7 @@
         <v>35</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>162</v>
+        <v>263</v>
       </c>
       <c r="C9" s="1" t="s">
         <v>32</v>
@@ -3489,12 +3811,12 @@
   <dimension ref="A1:F6"/>
   <sheetFormatPr defaultColWidth="9.19921875" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="1" width="9.19921875" style="1" collapsed="1"/>
-    <col min="2" max="2" width="27.73046875" style="1" bestFit="1" customWidth="1" collapsed="1"/>
-    <col min="3" max="3" width="15.796875" style="1" customWidth="1" collapsed="1"/>
-    <col min="4" max="4" width="50.796875" style="1" customWidth="1" collapsed="1"/>
-    <col min="5" max="5" width="46.265625" style="1" customWidth="1" collapsed="1"/>
-    <col min="6" max="16384" width="9.19921875" style="1" collapsed="1"/>
+    <col min="1" max="1" style="1" width="9.19921875" collapsed="true"/>
+    <col min="2" max="2" bestFit="true" customWidth="true" style="1" width="27.73046875" collapsed="true"/>
+    <col min="3" max="3" customWidth="true" style="1" width="15.796875" collapsed="true"/>
+    <col min="4" max="4" customWidth="true" style="1" width="50.796875" collapsed="true"/>
+    <col min="5" max="5" customWidth="true" style="1" width="46.265625" collapsed="true"/>
+    <col min="6" max="16384" style="1" width="9.19921875" collapsed="true"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.45">
@@ -3522,7 +3844,7 @@
         <v>35</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>152</v>
+        <v>264</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>32</v>
@@ -3542,7 +3864,7 @@
         <v>35</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>153</v>
+        <v>265</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>32</v>
@@ -3562,7 +3884,7 @@
         <v>35</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>154</v>
+        <v>266</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>32</v>
@@ -3582,7 +3904,7 @@
         <v>35</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>155</v>
+        <v>267</v>
       </c>
       <c r="C5" s="1" t="s">
         <v>32</v>
@@ -3602,7 +3924,7 @@
         <v>35</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>156</v>
+        <v>268</v>
       </c>
       <c r="C6" s="1" t="s">
         <v>32</v>
@@ -3627,12 +3949,12 @@
   <dimension ref="A1:E3"/>
   <sheetFormatPr defaultColWidth="9.19921875" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="1" width="9.19921875" style="1" collapsed="1"/>
-    <col min="2" max="2" width="22.46484375" style="1" customWidth="1" collapsed="1"/>
-    <col min="3" max="3" width="15.796875" style="1" customWidth="1" collapsed="1"/>
-    <col min="4" max="4" width="50.796875" style="1" customWidth="1" collapsed="1"/>
-    <col min="5" max="5" width="46.265625" style="1" customWidth="1" collapsed="1"/>
-    <col min="6" max="16384" width="9.19921875" style="1" collapsed="1"/>
+    <col min="1" max="1" style="1" width="9.19921875" collapsed="true"/>
+    <col min="2" max="2" customWidth="true" style="1" width="22.46484375" collapsed="true"/>
+    <col min="3" max="3" customWidth="true" style="1" width="15.796875" collapsed="true"/>
+    <col min="4" max="4" customWidth="true" style="1" width="50.796875" collapsed="true"/>
+    <col min="5" max="5" customWidth="true" style="1" width="46.265625" collapsed="true"/>
+    <col min="6" max="16384" style="1" width="9.19921875" collapsed="true"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.45">
@@ -3657,7 +3979,7 @@
         <v>35</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>146</v>
+        <v>255</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>32</v>

--- a/KatalonData/RADTestData/MRF.xlsx
+++ b/KatalonData/RADTestData/MRF.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr defaultThemeVersion="166925"/>
-  <mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\t465179\Documents\git\VPS-Katalon\VPS-Katalon\KatalonData\RADTestData\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8900DF63-5559-41AD-9BE5-EB63803DC3C0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{230548F7-5316-4BBE-B360-B48007D32CE6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3877" yWindow="3143" windowWidth="21601" windowHeight="11325" activeTab="5" xr2:uid="{D99FAB39-5CE6-4AA4-B9C6-99B1EFA0654E}"/>
+    <workbookView xWindow="5018" yWindow="3157" windowWidth="21600" windowHeight="11326" firstSheet="1" activeTab="7" xr2:uid="{D99FAB39-5CE6-4AA4-B9C6-99B1EFA0654E}"/>
   </bookViews>
   <sheets>
     <sheet name="Estimated" sheetId="1" r:id="rId1"/>
@@ -24,7 +24,7 @@
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
-    <ext uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
     </ext>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
@@ -43,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1211" uniqueCount="270">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="787" uniqueCount="163">
   <si>
     <t>Result</t>
   </si>
@@ -217,327 +217,6 @@
   </si>
   <si>
     <t>MFInsNum</t>
-  </si>
-  <si>
-    <t>Thu Jul 09 22:10:41 EDT 2026</t>
-  </si>
-  <si>
-    <t>Thu Jul 09 22:10:51 EDT 2026</t>
-  </si>
-  <si>
-    <t>Thu Jul 09 22:10:58 EDT 2026</t>
-  </si>
-  <si>
-    <t>Thu Jul 09 22:11:04 EDT 2026</t>
-  </si>
-  <si>
-    <t>Thu Jul 09 22:11:10 EDT 2026</t>
-  </si>
-  <si>
-    <t>Thu Jul 09 22:11:16 EDT 2026</t>
-  </si>
-  <si>
-    <t>Thu Jul 09 22:11:22 EDT 2026</t>
-  </si>
-  <si>
-    <t>Thu Jul 09 22:11:28 EDT 2026</t>
-  </si>
-  <si>
-    <t>Thu Jul 09 22:11:35 EDT 2026</t>
-  </si>
-  <si>
-    <t>Thu Jul 09 22:11:41 EDT 2026</t>
-  </si>
-  <si>
-    <t>Thu Jul 09 22:11:47 EDT 2026</t>
-  </si>
-  <si>
-    <t>Thu Jul 09 22:11:53 EDT 2026</t>
-  </si>
-  <si>
-    <t>Thu Jul 09 22:11:59 EDT 2026</t>
-  </si>
-  <si>
-    <t>Thu Jul 09 22:12:11 EDT 2026</t>
-  </si>
-  <si>
-    <t>Thu Jul 09 22:12:17 EDT 2026</t>
-  </si>
-  <si>
-    <t>Thu Jul 09 22:12:23 EDT 2026</t>
-  </si>
-  <si>
-    <t>Thu Jul 09 22:12:30 EDT 2026</t>
-  </si>
-  <si>
-    <t>Thu Jul 09 22:12:36 EDT 2026</t>
-  </si>
-  <si>
-    <t>Thu Jul 09 22:12:42 EDT 2026</t>
-  </si>
-  <si>
-    <t>Thu Jul 09 22:12:48 EDT 2026</t>
-  </si>
-  <si>
-    <t>Thu Jul 09 22:12:56 EDT 2026</t>
-  </si>
-  <si>
-    <t>Thu Jul 09 22:13:03 EDT 2026</t>
-  </si>
-  <si>
-    <t>Thu Jul 09 22:13:09 EDT 2026</t>
-  </si>
-  <si>
-    <t>Thu Jul 09 22:13:15 EDT 2026</t>
-  </si>
-  <si>
-    <t>Thu Jul 09 22:13:22 EDT 2026</t>
-  </si>
-  <si>
-    <t>Thu Jul 09 22:13:28 EDT 2026</t>
-  </si>
-  <si>
-    <t>Thu Jul 09 22:13:35 EDT 2026</t>
-  </si>
-  <si>
-    <t>Thu Jul 09 22:13:41 EDT 2026</t>
-  </si>
-  <si>
-    <t>Thu Jul 09 22:13:47 EDT 2026</t>
-  </si>
-  <si>
-    <t>Thu Jul 09 22:13:53 EDT 2026</t>
-  </si>
-  <si>
-    <t>Thu Jul 09 22:14:00 EDT 2026</t>
-  </si>
-  <si>
-    <t>Thu Jul 09 22:14:06 EDT 2026</t>
-  </si>
-  <si>
-    <t>Thu Jul 09 22:14:13 EDT 2026</t>
-  </si>
-  <si>
-    <t>Thu Jul 09 22:14:19 EDT 2026</t>
-  </si>
-  <si>
-    <t>Thu Jul 09 22:14:25 EDT 2026</t>
-  </si>
-  <si>
-    <t>Thu Jul 09 22:14:32 EDT 2026</t>
-  </si>
-  <si>
-    <t>Thu Jul 09 22:14:39 EDT 2026</t>
-  </si>
-  <si>
-    <t>Thu Jul 09 22:14:45 EDT 2026</t>
-  </si>
-  <si>
-    <t>Thu Jul 09 22:14:51 EDT 2026</t>
-  </si>
-  <si>
-    <t>Thu Jul 09 22:14:58 EDT 2026</t>
-  </si>
-  <si>
-    <t>Thu Jul 09 22:15:04 EDT 2026</t>
-  </si>
-  <si>
-    <t>Thu Jul 09 22:15:12 EDT 2026</t>
-  </si>
-  <si>
-    <t>Thu Jul 09 22:15:18 EDT 2026</t>
-  </si>
-  <si>
-    <t>Thu Jul 09 22:15:25 EDT 2026</t>
-  </si>
-  <si>
-    <t>Thu Jul 09 22:15:32 EDT 2026</t>
-  </si>
-  <si>
-    <t>Thu Jul 09 22:15:38 EDT 2026</t>
-  </si>
-  <si>
-    <t>Thu Jul 09 22:15:44 EDT 2026</t>
-  </si>
-  <si>
-    <t>Thu Jul 09 22:15:52 EDT 2026</t>
-  </si>
-  <si>
-    <t>Thu Jul 09 22:15:59 EDT 2026</t>
-  </si>
-  <si>
-    <t>Thu Jul 09 22:16:05 EDT 2026</t>
-  </si>
-  <si>
-    <t>Thu Jul 09 22:16:12 EDT 2026</t>
-  </si>
-  <si>
-    <t>Thu Jul 09 22:16:19 EDT 2026</t>
-  </si>
-  <si>
-    <t>Thu Jul 09 22:16:26 EDT 2026</t>
-  </si>
-  <si>
-    <t>Thu Jul 09 22:16:32 EDT 2026</t>
-  </si>
-  <si>
-    <t>Thu Jul 09 22:16:39 EDT 2026</t>
-  </si>
-  <si>
-    <t>Thu Jul 09 22:16:46 EDT 2026</t>
-  </si>
-  <si>
-    <t>Thu Jul 09 22:16:53 EDT 2026</t>
-  </si>
-  <si>
-    <t>Thu Jul 09 22:17:00 EDT 2026</t>
-  </si>
-  <si>
-    <t>Thu Jul 09 22:17:07 EDT 2026</t>
-  </si>
-  <si>
-    <t>Thu Jul 09 22:17:14 EDT 2026</t>
-  </si>
-  <si>
-    <t>Thu Jul 09 22:17:21 EDT 2026</t>
-  </si>
-  <si>
-    <t>Thu Jul 09 22:17:27 EDT 2026</t>
-  </si>
-  <si>
-    <t>Thu Jul 09 22:17:33 EDT 2026</t>
-  </si>
-  <si>
-    <t>Thu Jul 09 22:17:41 EDT 2026</t>
-  </si>
-  <si>
-    <t>Thu Jul 09 22:17:48 EDT 2026</t>
-  </si>
-  <si>
-    <t>Thu Jul 09 22:17:54 EDT 2026</t>
-  </si>
-  <si>
-    <t>Thu Jul 09 22:18:01 EDT 2026</t>
-  </si>
-  <si>
-    <t>Thu Jul 09 22:18:08 EDT 2026</t>
-  </si>
-  <si>
-    <t>Thu Jul 09 22:18:14 EDT 2026</t>
-  </si>
-  <si>
-    <t>Thu Jul 09 22:18:21 EDT 2026</t>
-  </si>
-  <si>
-    <t>Thu Jul 09 22:18:28 EDT 2026</t>
-  </si>
-  <si>
-    <t>Thu Jul 09 22:18:35 EDT 2026</t>
-  </si>
-  <si>
-    <t>Thu Jul 09 22:18:42 EDT 2026</t>
-  </si>
-  <si>
-    <t>Thu Jul 09 22:18:49 EDT 2026</t>
-  </si>
-  <si>
-    <t>Thu Jul 09 22:18:55 EDT 2026</t>
-  </si>
-  <si>
-    <t>Thu Jul 09 22:19:02 EDT 2026</t>
-  </si>
-  <si>
-    <t>Thu Jul 09 22:19:09 EDT 2026</t>
-  </si>
-  <si>
-    <t>Thu Jul 09 22:19:16 EDT 2026</t>
-  </si>
-  <si>
-    <t>Thu Jul 09 22:19:23 EDT 2026</t>
-  </si>
-  <si>
-    <t>Thu Jul 09 22:19:30 EDT 2026</t>
-  </si>
-  <si>
-    <t>Thu Jul 09 22:19:37 EDT 2026</t>
-  </si>
-  <si>
-    <t>Thu Jul 09 22:19:44 EDT 2026</t>
-  </si>
-  <si>
-    <t>Thu Jul 09 22:19:50 EDT 2026</t>
-  </si>
-  <si>
-    <t>Thu Jul 09 22:19:57 EDT 2026</t>
-  </si>
-  <si>
-    <t>Thu Jul 09 22:20:04 EDT 2026</t>
-  </si>
-  <si>
-    <t>Thu Jul 09 22:20:11 EDT 2026</t>
-  </si>
-  <si>
-    <t>Thu Jul 09 22:20:19 EDT 2026</t>
-  </si>
-  <si>
-    <t>Thu Jul 09 22:20:26 EDT 2026</t>
-  </si>
-  <si>
-    <t>Thu Jul 09 22:20:32 EDT 2026</t>
-  </si>
-  <si>
-    <t>Thu Jul 09 22:20:43 EDT 2026</t>
-  </si>
-  <si>
-    <t>Thu Jul 09 22:20:49 EDT 2026</t>
-  </si>
-  <si>
-    <t>Thu Jul 09 22:20:56 EDT 2026</t>
-  </si>
-  <si>
-    <t>Thu Jul 09 22:21:03 EDT 2026</t>
-  </si>
-  <si>
-    <t>Thu Jul 09 22:21:09 EDT 2026</t>
-  </si>
-  <si>
-    <t>Thu Jul 09 22:21:16 EDT 2026</t>
-  </si>
-  <si>
-    <t>Thu Jul 09 22:21:32 EDT 2026</t>
-  </si>
-  <si>
-    <t>Thu Jul 09 22:21:47 EDT 2026</t>
-  </si>
-  <si>
-    <t>Thu Jul 09 22:22:01 EDT 2026</t>
-  </si>
-  <si>
-    <t>Thu Jul 09 22:22:15 EDT 2026</t>
-  </si>
-  <si>
-    <t>Sun Aug 02 18:59:46 EDT 2026</t>
-  </si>
-  <si>
-    <t>Sun Aug 02 18:59:58 EDT 2026</t>
-  </si>
-  <si>
-    <t>Sun Aug 02 19:00:06 EDT 2026</t>
-  </si>
-  <si>
-    <t>Mon Aug 03 15:30:33 EDT 2026</t>
-  </si>
-  <si>
-    <t>Mon Aug 03 15:30:43 EDT 2026</t>
-  </si>
-  <si>
-    <t>Mon Aug 03 15:30:51 EDT 2026</t>
-  </si>
-  <si>
-    <t>Fail</t>
-  </si>
-  <si>
-    <t>Fri Sep 04 17:27:23 EDT 2026</t>
   </si>
   <si>
     <t>Fri Sep 04 17:27:35 EDT 2026</t>
@@ -859,7 +538,6 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="0"/>
   <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -1232,15 +910,15 @@
   <dimension ref="A1:H8"/>
   <sheetFormatPr defaultColWidth="9.19921875" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="1" style="1" width="9.19921875" collapsed="true"/>
-    <col min="2" max="2" bestFit="true" customWidth="true" style="1" width="26.73046875" collapsed="true"/>
-    <col min="3" max="3" style="1" width="9.19921875" collapsed="true"/>
-    <col min="4" max="4" customWidth="true" style="1" width="44.53125" collapsed="true"/>
-    <col min="5" max="5" customWidth="true" style="1" width="35.53125" collapsed="true"/>
-    <col min="6" max="6" customWidth="true" style="1" width="15.265625" collapsed="true"/>
-    <col min="7" max="7" customWidth="true" style="1" width="17.265625" collapsed="true"/>
-    <col min="8" max="8" customWidth="true" style="1" width="19.53125" collapsed="true"/>
-    <col min="9" max="16384" style="1" width="9.19921875" collapsed="true"/>
+    <col min="1" max="1" width="9.19921875" style="1" collapsed="1"/>
+    <col min="2" max="2" width="26.73046875" style="1" bestFit="1" customWidth="1" collapsed="1"/>
+    <col min="3" max="3" width="9.19921875" style="1" collapsed="1"/>
+    <col min="4" max="4" width="44.53125" style="1" customWidth="1" collapsed="1"/>
+    <col min="5" max="5" width="35.53125" style="1" customWidth="1" collapsed="1"/>
+    <col min="6" max="6" width="15.265625" style="1" customWidth="1" collapsed="1"/>
+    <col min="7" max="7" width="17.265625" style="1" customWidth="1" collapsed="1"/>
+    <col min="8" max="8" width="19.53125" style="1" customWidth="1" collapsed="1"/>
+    <col min="9" max="16384" width="9.19921875" style="1" collapsed="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.45">
@@ -1274,7 +952,7 @@
         <v>35</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>269</v>
+        <v>162</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>32</v>
@@ -1297,7 +975,7 @@
         <v>35</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>165</v>
+        <v>58</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>32</v>
@@ -1320,7 +998,7 @@
         <v>35</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>166</v>
+        <v>59</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>32</v>
@@ -1346,7 +1024,7 @@
         <v>35</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>167</v>
+        <v>60</v>
       </c>
       <c r="C5" s="1" t="s">
         <v>32</v>
@@ -1372,7 +1050,7 @@
         <v>35</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>168</v>
+        <v>61</v>
       </c>
       <c r="C6" s="1" t="s">
         <v>32</v>
@@ -1398,7 +1076,7 @@
         <v>35</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>169</v>
+        <v>62</v>
       </c>
       <c r="C7" s="1" t="s">
         <v>32</v>
@@ -1424,7 +1102,7 @@
         <v>35</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>170</v>
+        <v>63</v>
       </c>
       <c r="C8" s="1" t="s">
         <v>32</v>
@@ -1457,14 +1135,14 @@
   <dimension ref="A1:H21"/>
   <sheetFormatPr defaultColWidth="9.19921875" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="1" customWidth="true" style="1" width="14.53125" collapsed="true"/>
-    <col min="2" max="2" bestFit="true" customWidth="true" style="1" width="26.73046875" collapsed="true"/>
-    <col min="3" max="3" customWidth="true" style="1" width="13.46484375" collapsed="true"/>
-    <col min="4" max="4" customWidth="true" style="1" width="52.46484375" collapsed="true"/>
-    <col min="5" max="5" customWidth="true" style="1" width="32.46484375" collapsed="true"/>
-    <col min="6" max="7" style="1" width="9.19921875" collapsed="true"/>
-    <col min="8" max="8" customWidth="true" style="1" width="13.0" collapsed="true"/>
-    <col min="9" max="16384" style="1" width="9.19921875" collapsed="true"/>
+    <col min="1" max="1" width="14.53125" style="1" customWidth="1" collapsed="1"/>
+    <col min="2" max="2" width="26.73046875" style="1" bestFit="1" customWidth="1" collapsed="1"/>
+    <col min="3" max="3" width="13.46484375" style="1" customWidth="1" collapsed="1"/>
+    <col min="4" max="4" width="52.46484375" style="1" customWidth="1" collapsed="1"/>
+    <col min="5" max="5" width="32.46484375" style="1" customWidth="1" collapsed="1"/>
+    <col min="6" max="7" width="9.19921875" style="1" collapsed="1"/>
+    <col min="8" max="8" width="13" style="1" customWidth="1" collapsed="1"/>
+    <col min="9" max="16384" width="9.19921875" style="1" collapsed="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.45">
@@ -1498,7 +1176,7 @@
         <v>35</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>171</v>
+        <v>64</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>32</v>
@@ -1515,7 +1193,7 @@
         <v>35</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>172</v>
+        <v>65</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>32</v>
@@ -1532,7 +1210,7 @@
         <v>35</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>173</v>
+        <v>66</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>32</v>
@@ -1549,7 +1227,7 @@
         <v>35</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>174</v>
+        <v>67</v>
       </c>
       <c r="C5" s="1" t="s">
         <v>32</v>
@@ -1569,7 +1247,7 @@
         <v>35</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>175</v>
+        <v>68</v>
       </c>
       <c r="C6" s="1" t="s">
         <v>32</v>
@@ -1589,7 +1267,7 @@
         <v>35</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>176</v>
+        <v>69</v>
       </c>
       <c r="C7" s="1" t="s">
         <v>32</v>
@@ -1609,7 +1287,7 @@
         <v>35</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>177</v>
+        <v>70</v>
       </c>
       <c r="C8" s="1" t="s">
         <v>32</v>
@@ -1629,7 +1307,7 @@
         <v>35</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>178</v>
+        <v>71</v>
       </c>
       <c r="C9" s="1" t="s">
         <v>32</v>
@@ -1649,7 +1327,7 @@
         <v>35</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>179</v>
+        <v>72</v>
       </c>
       <c r="C10" s="1" t="s">
         <v>32</v>
@@ -1669,7 +1347,7 @@
         <v>35</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>180</v>
+        <v>73</v>
       </c>
       <c r="C11" s="1" t="s">
         <v>32</v>
@@ -1689,7 +1367,7 @@
         <v>35</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>181</v>
+        <v>74</v>
       </c>
       <c r="C12" s="1" t="s">
         <v>32</v>
@@ -1709,7 +1387,7 @@
         <v>35</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>182</v>
+        <v>75</v>
       </c>
       <c r="C13" s="1" t="s">
         <v>32</v>
@@ -1729,7 +1407,7 @@
         <v>35</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>183</v>
+        <v>76</v>
       </c>
       <c r="C14" s="1" t="s">
         <v>32</v>
@@ -1749,7 +1427,7 @@
         <v>35</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>184</v>
+        <v>77</v>
       </c>
       <c r="C15" s="1" t="s">
         <v>32</v>
@@ -1766,7 +1444,7 @@
         <v>35</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>185</v>
+        <v>78</v>
       </c>
       <c r="C16" s="1" t="s">
         <v>32</v>
@@ -1789,7 +1467,7 @@
         <v>35</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>186</v>
+        <v>79</v>
       </c>
       <c r="C17" s="1" t="s">
         <v>32</v>
@@ -1809,7 +1487,7 @@
         <v>35</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>187</v>
+        <v>80</v>
       </c>
       <c r="C18" s="1" t="s">
         <v>32</v>
@@ -1837,7 +1515,7 @@
         <v>35</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>188</v>
+        <v>81</v>
       </c>
       <c r="C20" s="1" t="s">
         <v>32</v>
@@ -1876,15 +1554,15 @@
   <dimension ref="A1:H7"/>
   <sheetFormatPr defaultColWidth="9.19921875" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="1" style="1" width="9.19921875" collapsed="true"/>
-    <col min="2" max="2" customWidth="true" style="1" width="35.0" collapsed="true"/>
-    <col min="3" max="3" customWidth="true" style="1" width="19.19921875" collapsed="true"/>
-    <col min="4" max="4" customWidth="true" style="1" width="24.46484375" collapsed="true"/>
-    <col min="5" max="5" bestFit="true" customWidth="true" style="1" width="27.0" collapsed="true"/>
-    <col min="6" max="6" style="1" width="9.19921875" collapsed="true"/>
-    <col min="7" max="7" customWidth="true" style="1" width="17.0" collapsed="true"/>
-    <col min="8" max="8" customWidth="true" style="1" width="16.265625" collapsed="true"/>
-    <col min="9" max="16384" style="1" width="9.19921875" collapsed="true"/>
+    <col min="1" max="1" width="9.19921875" style="1" collapsed="1"/>
+    <col min="2" max="2" width="35" style="1" customWidth="1" collapsed="1"/>
+    <col min="3" max="3" width="19.19921875" style="1" customWidth="1" collapsed="1"/>
+    <col min="4" max="4" width="24.46484375" style="1" customWidth="1" collapsed="1"/>
+    <col min="5" max="5" width="27" style="1" bestFit="1" customWidth="1" collapsed="1"/>
+    <col min="6" max="6" width="9.19921875" style="1" collapsed="1"/>
+    <col min="7" max="7" width="17" style="1" customWidth="1" collapsed="1"/>
+    <col min="8" max="8" width="16.265625" style="1" customWidth="1" collapsed="1"/>
+    <col min="9" max="16384" width="9.19921875" style="1" collapsed="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.45">
@@ -1918,7 +1596,7 @@
         <v>35</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>189</v>
+        <v>82</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>32</v>
@@ -1941,7 +1619,7 @@
         <v>35</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>190</v>
+        <v>83</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>32</v>
@@ -1961,7 +1639,7 @@
         <v>35</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>191</v>
+        <v>84</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>32</v>
@@ -1984,7 +1662,7 @@
         <v>35</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>192</v>
+        <v>85</v>
       </c>
       <c r="C5" s="1" t="s">
         <v>32</v>
@@ -2007,7 +1685,7 @@
         <v>35</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>193</v>
+        <v>86</v>
       </c>
       <c r="C6" s="1" t="s">
         <v>32</v>
@@ -2030,7 +1708,7 @@
         <v>35</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>194</v>
+        <v>87</v>
       </c>
       <c r="C7" s="1" t="s">
         <v>32</v>
@@ -2062,17 +1740,17 @@
   <dimension ref="A1:J64"/>
   <sheetFormatPr defaultColWidth="9.19921875" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="1" style="1" width="9.19921875" collapsed="true"/>
-    <col min="2" max="2" bestFit="true" customWidth="true" style="1" width="26.0" collapsed="true"/>
-    <col min="3" max="3" customWidth="true" style="1" width="12.33203125" collapsed="true"/>
-    <col min="4" max="4" customWidth="true" style="1" width="31.73046875" collapsed="true"/>
-    <col min="5" max="5" customWidth="true" style="1" width="39.53125" collapsed="true"/>
-    <col min="6" max="6" style="1" width="9.19921875" collapsed="true"/>
-    <col min="7" max="7" customWidth="true" style="1" width="19.796875" collapsed="true"/>
-    <col min="8" max="8" customWidth="true" style="1" width="14.46484375" collapsed="true"/>
-    <col min="9" max="9" customWidth="true" style="1" width="12.73046875" collapsed="true"/>
-    <col min="10" max="10" customWidth="true" style="1" width="11.19921875" collapsed="true"/>
-    <col min="11" max="16384" style="1" width="9.19921875" collapsed="true"/>
+    <col min="1" max="1" width="9.19921875" style="1" collapsed="1"/>
+    <col min="2" max="2" width="26" style="1" bestFit="1" customWidth="1" collapsed="1"/>
+    <col min="3" max="3" width="12.33203125" style="1" customWidth="1" collapsed="1"/>
+    <col min="4" max="4" width="31.73046875" style="1" customWidth="1" collapsed="1"/>
+    <col min="5" max="5" width="39.53125" style="1" customWidth="1" collapsed="1"/>
+    <col min="6" max="6" width="9.19921875" style="1" collapsed="1"/>
+    <col min="7" max="7" width="19.796875" style="1" customWidth="1" collapsed="1"/>
+    <col min="8" max="8" width="14.46484375" style="1" customWidth="1" collapsed="1"/>
+    <col min="9" max="9" width="12.73046875" style="1" customWidth="1" collapsed="1"/>
+    <col min="10" max="10" width="11.19921875" style="1" customWidth="1" collapsed="1"/>
+    <col min="11" max="16384" width="9.19921875" style="1" collapsed="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:10" x14ac:dyDescent="0.45">
@@ -2112,7 +1790,7 @@
         <v>35</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>195</v>
+        <v>88</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>32</v>
@@ -2132,7 +1810,7 @@
         <v>35</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>196</v>
+        <v>89</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>32</v>
@@ -2155,7 +1833,7 @@
         <v>35</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>197</v>
+        <v>90</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>32</v>
@@ -2178,7 +1856,7 @@
         <v>35</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>198</v>
+        <v>91</v>
       </c>
       <c r="C5" s="1" t="s">
         <v>32</v>
@@ -2201,7 +1879,7 @@
         <v>35</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>199</v>
+        <v>92</v>
       </c>
       <c r="C6" s="1" t="s">
         <v>32</v>
@@ -2224,7 +1902,7 @@
         <v>35</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>200</v>
+        <v>93</v>
       </c>
       <c r="C7" s="1" t="s">
         <v>32</v>
@@ -2244,7 +1922,7 @@
         <v>35</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>201</v>
+        <v>94</v>
       </c>
       <c r="C8" s="1" t="s">
         <v>32</v>
@@ -2267,7 +1945,7 @@
         <v>35</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>202</v>
+        <v>95</v>
       </c>
       <c r="C9" s="1" t="s">
         <v>32</v>
@@ -2290,7 +1968,7 @@
         <v>35</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>203</v>
+        <v>96</v>
       </c>
       <c r="C10" s="1" t="s">
         <v>32</v>
@@ -2313,7 +1991,7 @@
         <v>35</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>204</v>
+        <v>97</v>
       </c>
       <c r="C11" s="1" t="s">
         <v>32</v>
@@ -2336,7 +2014,7 @@
         <v>35</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>205</v>
+        <v>98</v>
       </c>
       <c r="C12" s="1" t="s">
         <v>32</v>
@@ -2356,7 +2034,7 @@
         <v>35</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>206</v>
+        <v>99</v>
       </c>
       <c r="C13" s="1" t="s">
         <v>32</v>
@@ -2379,7 +2057,7 @@
         <v>35</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>207</v>
+        <v>100</v>
       </c>
       <c r="C14" s="1" t="s">
         <v>32</v>
@@ -2402,7 +2080,7 @@
         <v>35</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>208</v>
+        <v>101</v>
       </c>
       <c r="C15" s="1" t="s">
         <v>32</v>
@@ -2425,7 +2103,7 @@
         <v>35</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>209</v>
+        <v>102</v>
       </c>
       <c r="C16" s="1" t="s">
         <v>32</v>
@@ -2448,7 +2126,7 @@
         <v>35</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>210</v>
+        <v>103</v>
       </c>
       <c r="C17" s="1" t="s">
         <v>32</v>
@@ -2471,7 +2149,7 @@
         <v>35</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>211</v>
+        <v>104</v>
       </c>
       <c r="C18" s="1" t="s">
         <v>32</v>
@@ -2494,7 +2172,7 @@
         <v>35</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>212</v>
+        <v>105</v>
       </c>
       <c r="C19" s="1" t="s">
         <v>32</v>
@@ -2514,7 +2192,7 @@
         <v>35</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>213</v>
+        <v>106</v>
       </c>
       <c r="C20" s="1" t="s">
         <v>32</v>
@@ -2534,7 +2212,7 @@
         <v>35</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>214</v>
+        <v>107</v>
       </c>
       <c r="C21" s="1" t="s">
         <v>32</v>
@@ -2557,7 +2235,7 @@
         <v>35</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>215</v>
+        <v>108</v>
       </c>
       <c r="C22" s="1" t="s">
         <v>32</v>
@@ -2580,7 +2258,7 @@
         <v>35</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>216</v>
+        <v>109</v>
       </c>
       <c r="C23" s="1" t="s">
         <v>32</v>
@@ -2600,7 +2278,7 @@
         <v>35</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>217</v>
+        <v>110</v>
       </c>
       <c r="C24" s="1" t="s">
         <v>32</v>
@@ -2623,7 +2301,7 @@
         <v>35</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>218</v>
+        <v>111</v>
       </c>
       <c r="C25" s="1" t="s">
         <v>32</v>
@@ -2649,7 +2327,7 @@
         <v>35</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>219</v>
+        <v>112</v>
       </c>
       <c r="C26" s="1" t="s">
         <v>32</v>
@@ -2672,7 +2350,7 @@
         <v>35</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>220</v>
+        <v>113</v>
       </c>
       <c r="C27" s="1" t="s">
         <v>32</v>
@@ -2692,7 +2370,7 @@
         <v>35</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>221</v>
+        <v>114</v>
       </c>
       <c r="C28" s="1" t="s">
         <v>32</v>
@@ -2715,7 +2393,7 @@
         <v>35</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>222</v>
+        <v>115</v>
       </c>
       <c r="C29" s="1" t="s">
         <v>32</v>
@@ -2738,7 +2416,7 @@
         <v>35</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>223</v>
+        <v>116</v>
       </c>
       <c r="C30" s="1" t="s">
         <v>32</v>
@@ -2761,7 +2439,7 @@
         <v>35</v>
       </c>
       <c r="B31" s="1" t="s">
-        <v>224</v>
+        <v>117</v>
       </c>
       <c r="C31" s="1" t="s">
         <v>32</v>
@@ -2781,7 +2459,7 @@
         <v>35</v>
       </c>
       <c r="B32" s="1" t="s">
-        <v>225</v>
+        <v>118</v>
       </c>
       <c r="C32" s="1" t="s">
         <v>32</v>
@@ -2801,7 +2479,7 @@
         <v>35</v>
       </c>
       <c r="B33" s="1" t="s">
-        <v>226</v>
+        <v>119</v>
       </c>
       <c r="C33" s="1" t="s">
         <v>32</v>
@@ -2824,7 +2502,7 @@
         <v>35</v>
       </c>
       <c r="B34" s="1" t="s">
-        <v>227</v>
+        <v>120</v>
       </c>
       <c r="C34" s="1" t="s">
         <v>32</v>
@@ -2847,7 +2525,7 @@
         <v>35</v>
       </c>
       <c r="B35" s="1" t="s">
-        <v>228</v>
+        <v>121</v>
       </c>
       <c r="C35" s="1" t="s">
         <v>32</v>
@@ -2867,7 +2545,7 @@
         <v>35</v>
       </c>
       <c r="B36" s="1" t="s">
-        <v>229</v>
+        <v>122</v>
       </c>
       <c r="C36" s="1" t="s">
         <v>32</v>
@@ -2890,7 +2568,7 @@
         <v>35</v>
       </c>
       <c r="B37" s="1" t="s">
-        <v>230</v>
+        <v>123</v>
       </c>
       <c r="C37" s="1" t="s">
         <v>32</v>
@@ -2916,7 +2594,7 @@
         <v>35</v>
       </c>
       <c r="B38" s="1" t="s">
-        <v>231</v>
+        <v>124</v>
       </c>
       <c r="C38" s="1" t="s">
         <v>32</v>
@@ -2939,7 +2617,7 @@
         <v>35</v>
       </c>
       <c r="B39" s="1" t="s">
-        <v>232</v>
+        <v>125</v>
       </c>
       <c r="C39" s="1" t="s">
         <v>32</v>
@@ -2959,7 +2637,7 @@
         <v>35</v>
       </c>
       <c r="B40" s="1" t="s">
-        <v>233</v>
+        <v>126</v>
       </c>
       <c r="C40" s="1" t="s">
         <v>32</v>
@@ -2982,7 +2660,7 @@
         <v>35</v>
       </c>
       <c r="B41" s="1" t="s">
-        <v>234</v>
+        <v>127</v>
       </c>
       <c r="C41" s="1" t="s">
         <v>32</v>
@@ -3005,7 +2683,7 @@
         <v>35</v>
       </c>
       <c r="B42" s="1" t="s">
-        <v>235</v>
+        <v>128</v>
       </c>
       <c r="C42" s="1" t="s">
         <v>32</v>
@@ -3028,7 +2706,7 @@
         <v>35</v>
       </c>
       <c r="B43" s="1" t="s">
-        <v>236</v>
+        <v>129</v>
       </c>
       <c r="C43" s="1" t="s">
         <v>32</v>
@@ -3048,7 +2726,7 @@
         <v>35</v>
       </c>
       <c r="B44" s="1" t="s">
-        <v>237</v>
+        <v>130</v>
       </c>
       <c r="C44" s="1" t="s">
         <v>32</v>
@@ -3068,7 +2746,7 @@
         <v>35</v>
       </c>
       <c r="B45" s="1" t="s">
-        <v>238</v>
+        <v>131</v>
       </c>
       <c r="C45" s="1" t="s">
         <v>32</v>
@@ -3091,7 +2769,7 @@
         <v>35</v>
       </c>
       <c r="B46" s="1" t="s">
-        <v>239</v>
+        <v>132</v>
       </c>
       <c r="C46" s="1" t="s">
         <v>32</v>
@@ -3114,7 +2792,7 @@
         <v>35</v>
       </c>
       <c r="B47" s="1" t="s">
-        <v>240</v>
+        <v>133</v>
       </c>
       <c r="C47" s="1" t="s">
         <v>32</v>
@@ -3134,7 +2812,7 @@
         <v>35</v>
       </c>
       <c r="B48" s="1" t="s">
-        <v>241</v>
+        <v>134</v>
       </c>
       <c r="C48" s="1" t="s">
         <v>32</v>
@@ -3157,7 +2835,7 @@
         <v>35</v>
       </c>
       <c r="B49" s="1" t="s">
-        <v>242</v>
+        <v>135</v>
       </c>
       <c r="C49" s="1" t="s">
         <v>32</v>
@@ -3183,7 +2861,7 @@
         <v>35</v>
       </c>
       <c r="B50" s="1" t="s">
-        <v>243</v>
+        <v>136</v>
       </c>
       <c r="C50" s="1" t="s">
         <v>32</v>
@@ -3206,7 +2884,7 @@
         <v>35</v>
       </c>
       <c r="B51" s="1" t="s">
-        <v>244</v>
+        <v>137</v>
       </c>
       <c r="C51" s="1" t="s">
         <v>32</v>
@@ -3226,7 +2904,7 @@
         <v>35</v>
       </c>
       <c r="B52" s="1" t="s">
-        <v>245</v>
+        <v>138</v>
       </c>
       <c r="C52" s="1" t="s">
         <v>32</v>
@@ -3249,7 +2927,7 @@
         <v>35</v>
       </c>
       <c r="B53" s="1" t="s">
-        <v>246</v>
+        <v>139</v>
       </c>
       <c r="C53" s="1" t="s">
         <v>32</v>
@@ -3269,7 +2947,7 @@
         <v>35</v>
       </c>
       <c r="B54" s="1" t="s">
-        <v>247</v>
+        <v>140</v>
       </c>
       <c r="C54" s="1" t="s">
         <v>32</v>
@@ -3309,7 +2987,7 @@
         <v>35</v>
       </c>
       <c r="B56" s="1" t="s">
-        <v>248</v>
+        <v>141</v>
       </c>
       <c r="C56" s="1" t="s">
         <v>32</v>
@@ -3329,7 +3007,7 @@
         <v>35</v>
       </c>
       <c r="B57" s="1" t="s">
-        <v>249</v>
+        <v>142</v>
       </c>
       <c r="C57" s="1" t="s">
         <v>32</v>
@@ -3369,7 +3047,7 @@
         <v>35</v>
       </c>
       <c r="B59" s="1" t="s">
-        <v>250</v>
+        <v>143</v>
       </c>
       <c r="C59" s="1" t="s">
         <v>32</v>
@@ -3389,7 +3067,7 @@
         <v>35</v>
       </c>
       <c r="B60" s="1" t="s">
-        <v>251</v>
+        <v>144</v>
       </c>
       <c r="C60" s="1" t="s">
         <v>32</v>
@@ -3429,7 +3107,7 @@
         <v>35</v>
       </c>
       <c r="B62" s="1" t="s">
-        <v>252</v>
+        <v>145</v>
       </c>
       <c r="C62" s="1" t="s">
         <v>32</v>
@@ -3452,7 +3130,7 @@
         <v>35</v>
       </c>
       <c r="B63" s="1" t="s">
-        <v>253</v>
+        <v>146</v>
       </c>
       <c r="C63" s="1" t="s">
         <v>32</v>
@@ -3475,7 +3153,7 @@
         <v>35</v>
       </c>
       <c r="B64" s="1" t="s">
-        <v>254</v>
+        <v>147</v>
       </c>
       <c r="C64" s="1" t="s">
         <v>32</v>
@@ -3506,12 +3184,12 @@
   <dimension ref="A1:F7"/>
   <sheetFormatPr defaultColWidth="9.19921875" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="1" style="1" width="9.19921875" collapsed="true"/>
-    <col min="2" max="2" customWidth="true" style="1" width="22.46484375" collapsed="true"/>
-    <col min="3" max="3" customWidth="true" style="1" width="17.265625" collapsed="true"/>
-    <col min="4" max="4" customWidth="true" style="1" width="50.796875" collapsed="true"/>
-    <col min="5" max="5" customWidth="true" style="1" width="46.265625" collapsed="true"/>
-    <col min="6" max="16384" style="1" width="9.19921875" collapsed="true"/>
+    <col min="1" max="1" width="9.19921875" style="1" collapsed="1"/>
+    <col min="2" max="2" width="22.46484375" style="1" customWidth="1" collapsed="1"/>
+    <col min="3" max="3" width="17.265625" style="1" customWidth="1" collapsed="1"/>
+    <col min="4" max="4" width="50.796875" style="1" customWidth="1" collapsed="1"/>
+    <col min="5" max="5" width="46.265625" style="1" customWidth="1" collapsed="1"/>
+    <col min="6" max="16384" width="9.19921875" style="1" collapsed="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.45">
@@ -3613,12 +3291,12 @@
   <dimension ref="A1:F9"/>
   <sheetFormatPr defaultColWidth="9.19921875" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="1" bestFit="true" customWidth="true" style="1" width="6.53125" collapsed="true"/>
-    <col min="2" max="2" bestFit="true" customWidth="true" style="1" width="26.46484375" collapsed="true"/>
-    <col min="3" max="3" customWidth="true" style="1" width="14.796875" collapsed="true"/>
-    <col min="4" max="4" customWidth="true" style="1" width="50.796875" collapsed="true"/>
-    <col min="5" max="5" customWidth="true" style="1" width="46.265625" collapsed="true"/>
-    <col min="6" max="16384" style="1" width="9.19921875" collapsed="true"/>
+    <col min="1" max="1" width="6.53125" style="1" bestFit="1" customWidth="1" collapsed="1"/>
+    <col min="2" max="2" width="26.46484375" style="1" bestFit="1" customWidth="1" collapsed="1"/>
+    <col min="3" max="3" width="14.796875" style="1" customWidth="1" collapsed="1"/>
+    <col min="4" max="4" width="50.796875" style="1" customWidth="1" collapsed="1"/>
+    <col min="5" max="5" width="46.265625" style="1" customWidth="1" collapsed="1"/>
+    <col min="6" max="16384" width="9.19921875" style="1" collapsed="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.45">
@@ -3646,7 +3324,7 @@
         <v>35</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>256</v>
+        <v>149</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>32</v>
@@ -3666,7 +3344,7 @@
         <v>35</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>257</v>
+        <v>150</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>32</v>
@@ -3686,7 +3364,7 @@
         <v>35</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>258</v>
+        <v>151</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>32</v>
@@ -3706,7 +3384,7 @@
         <v>35</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>259</v>
+        <v>152</v>
       </c>
       <c r="C5" s="1" t="s">
         <v>32</v>
@@ -3726,7 +3404,7 @@
         <v>35</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>260</v>
+        <v>153</v>
       </c>
       <c r="C6" s="1" t="s">
         <v>32</v>
@@ -3746,7 +3424,7 @@
         <v>35</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>261</v>
+        <v>154</v>
       </c>
       <c r="C7" s="1" t="s">
         <v>32</v>
@@ -3766,7 +3444,7 @@
         <v>35</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>262</v>
+        <v>155</v>
       </c>
       <c r="C8" s="1" t="s">
         <v>32</v>
@@ -3786,7 +3464,7 @@
         <v>35</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>263</v>
+        <v>156</v>
       </c>
       <c r="C9" s="1" t="s">
         <v>32</v>
@@ -3811,12 +3489,12 @@
   <dimension ref="A1:F6"/>
   <sheetFormatPr defaultColWidth="9.19921875" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="1" style="1" width="9.19921875" collapsed="true"/>
-    <col min="2" max="2" bestFit="true" customWidth="true" style="1" width="27.73046875" collapsed="true"/>
-    <col min="3" max="3" customWidth="true" style="1" width="15.796875" collapsed="true"/>
-    <col min="4" max="4" customWidth="true" style="1" width="50.796875" collapsed="true"/>
-    <col min="5" max="5" customWidth="true" style="1" width="46.265625" collapsed="true"/>
-    <col min="6" max="16384" style="1" width="9.19921875" collapsed="true"/>
+    <col min="1" max="1" width="9.19921875" style="1" collapsed="1"/>
+    <col min="2" max="2" width="27.73046875" style="1" bestFit="1" customWidth="1" collapsed="1"/>
+    <col min="3" max="3" width="15.796875" style="1" customWidth="1" collapsed="1"/>
+    <col min="4" max="4" width="50.796875" style="1" customWidth="1" collapsed="1"/>
+    <col min="5" max="5" width="46.265625" style="1" customWidth="1" collapsed="1"/>
+    <col min="6" max="16384" width="9.19921875" style="1" collapsed="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.45">
@@ -3844,7 +3522,7 @@
         <v>35</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>264</v>
+        <v>157</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>32</v>
@@ -3864,7 +3542,7 @@
         <v>35</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>265</v>
+        <v>158</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>32</v>
@@ -3884,7 +3562,7 @@
         <v>35</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>266</v>
+        <v>159</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>32</v>
@@ -3904,7 +3582,7 @@
         <v>35</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>267</v>
+        <v>160</v>
       </c>
       <c r="C5" s="1" t="s">
         <v>32</v>
@@ -3924,7 +3602,7 @@
         <v>35</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>268</v>
+        <v>161</v>
       </c>
       <c r="C6" s="1" t="s">
         <v>32</v>
@@ -3949,12 +3627,12 @@
   <dimension ref="A1:E3"/>
   <sheetFormatPr defaultColWidth="9.19921875" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="1" style="1" width="9.19921875" collapsed="true"/>
-    <col min="2" max="2" customWidth="true" style="1" width="22.46484375" collapsed="true"/>
-    <col min="3" max="3" customWidth="true" style="1" width="15.796875" collapsed="true"/>
-    <col min="4" max="4" customWidth="true" style="1" width="50.796875" collapsed="true"/>
-    <col min="5" max="5" customWidth="true" style="1" width="46.265625" collapsed="true"/>
-    <col min="6" max="16384" style="1" width="9.19921875" collapsed="true"/>
+    <col min="1" max="1" width="9.19921875" style="1" collapsed="1"/>
+    <col min="2" max="2" width="28.33203125" style="1" customWidth="1" collapsed="1"/>
+    <col min="3" max="3" width="15.796875" style="1" customWidth="1" collapsed="1"/>
+    <col min="4" max="4" width="50.796875" style="1" customWidth="1" collapsed="1"/>
+    <col min="5" max="5" width="46.265625" style="1" customWidth="1" collapsed="1"/>
+    <col min="6" max="16384" width="9.19921875" style="1" collapsed="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.45">
@@ -3974,12 +3652,12 @@
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:5" ht="28.5" x14ac:dyDescent="0.45">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A2" s="1" t="s">
         <v>35</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>255</v>
+        <v>148</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>32</v>
@@ -3991,7 +3669,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="3" spans="1:5" ht="28.5" x14ac:dyDescent="0.45">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A3" s="1" t="s">
         <v>35</v>
       </c>
